--- a/12623065.xlsx
+++ b/12623065.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -141,7 +141,7 @@
     <t>Month:</t>
   </si>
   <si>
-    <t>September</t>
+    <t>August</t>
   </si>
   <si>
     <t>All durations in MINUTES. Yellow cells = enter your data. Row 6 is a sample — overwrite it. Rows 2-3: fill your details.</t>

--- a/12623065.xlsx
+++ b/12623065.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -141,7 +141,7 @@
     <t>Month:</t>
   </si>
   <si>
-    <t>August</t>
+    <t>September</t>
   </si>
   <si>
     <t>All durations in MINUTES. Yellow cells = enter your data. Row 6 is a sample — overwrite it. Rows 2-3: fill your details.</t>
@@ -201,46 +201,46 @@
     <t>Example row — replace with your own data. Felt a bit tired after evening class.</t>
   </si>
   <si>
-    <t>Overall it was a good day</t>
+    <t>Overall it was a good day.</t>
   </si>
   <si>
-    <t>Attend all my classes</t>
+    <t>Attend all my classes.</t>
   </si>
   <si>
     <t>Neutral</t>
   </si>
   <si>
-    <t>Revised today's topics</t>
+    <t>Revised today's topics.</t>
   </si>
   <si>
-    <t xml:space="preserve">Focused well on my </t>
+    <t>Focused well on my  work.</t>
   </si>
   <si>
-    <t>Had a positive day</t>
+    <t>Had a positive day.</t>
   </si>
   <si>
-    <t>Took sometime to rest</t>
+    <t>Took sometime to rest.</t>
   </si>
   <si>
-    <t>It was good day</t>
+    <t>It was good day.</t>
   </si>
   <si>
-    <t>Had a busy day</t>
+    <t>Had a busy day.</t>
   </si>
   <si>
-    <t>Need to revise today's work</t>
+    <t>Need to revise today's work.</t>
   </si>
   <si>
-    <t>Learned from my mistakes</t>
+    <t>Learned from my mistakes.</t>
   </si>
   <si>
-    <t>Had a normal day</t>
+    <t>Had a normal day.</t>
   </si>
   <si>
-    <t>Felt motivate to learn</t>
+    <t>Felt motivate to learn.</t>
   </si>
   <si>
-    <t>Spent time on my hoobies</t>
+    <t>Spent time on my hoobies.</t>
   </si>
   <si>
     <t>Practice coding today</t>
@@ -249,22 +249,22 @@
     <t>Focused well on my studies</t>
   </si>
   <si>
-    <t xml:space="preserve">Need to focus more </t>
+    <t>Need to focus more .</t>
   </si>
   <si>
-    <t>Manage my time well today</t>
+    <t>Manage my time well today.</t>
   </si>
   <si>
-    <t>Stayed focus on my goals</t>
+    <t>Stayed focus on my goals.</t>
   </si>
   <si>
-    <t>Completed my routine</t>
+    <t>Completed my routine.</t>
   </si>
   <si>
-    <t>Had a peacefull day</t>
+    <t>Had a peacefull day.</t>
   </si>
   <si>
-    <t>Good use of time</t>
+    <t>Good use of time.</t>
   </si>
 </sst>
 </file>
@@ -1733,7 +1733,7 @@
         <v>180</v>
       </c>
       <c r="E7" s="12">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F7" s="12">
         <v>250</v>
@@ -1746,11 +1746,11 @@
       </c>
       <c r="I7" s="13">
         <f t="shared" si="0"/>
-        <v>930</v>
+        <v>950</v>
       </c>
       <c r="J7" s="13">
         <f t="shared" si="1"/>
-        <v>510</v>
+        <v>490</v>
       </c>
       <c r="K7" s="14" t="s">
         <v>53</v>
@@ -1779,7 +1779,7 @@
         <v>120</v>
       </c>
       <c r="E8" s="12">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F8" s="12">
         <v>250</v>
@@ -1792,11 +1792,11 @@
       </c>
       <c r="I8" s="13">
         <f t="shared" si="0"/>
-        <v>860</v>
+        <v>890</v>
       </c>
       <c r="J8" s="13">
         <f t="shared" si="1"/>
-        <v>580</v>
+        <v>550</v>
       </c>
       <c r="K8" s="14" t="s">
         <v>53</v>
@@ -1825,7 +1825,7 @@
         <v>180</v>
       </c>
       <c r="E9" s="12">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F9" s="12">
         <v>250</v>
@@ -1838,11 +1838,11 @@
       </c>
       <c r="I9" s="13">
         <f t="shared" si="0"/>
-        <v>910</v>
+        <v>920</v>
       </c>
       <c r="J9" s="13">
         <f t="shared" si="1"/>
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="K9" s="14" t="s">
         <v>59</v>
@@ -1871,7 +1871,7 @@
         <v>240</v>
       </c>
       <c r="E10" s="12">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="F10" s="12">
         <v>150</v>
@@ -1884,11 +1884,11 @@
       </c>
       <c r="I10" s="13">
         <f t="shared" si="0"/>
-        <v>880</v>
+        <v>920</v>
       </c>
       <c r="J10" s="13">
         <f t="shared" si="1"/>
-        <v>560</v>
+        <v>520</v>
       </c>
       <c r="K10" s="14" t="s">
         <v>53</v>
@@ -1917,7 +1917,7 @@
         <v>180</v>
       </c>
       <c r="E11" s="12">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F11" s="12">
         <v>150</v>
@@ -1930,11 +1930,11 @@
       </c>
       <c r="I11" s="13">
         <f t="shared" si="0"/>
-        <v>820</v>
+        <v>830</v>
       </c>
       <c r="J11" s="13">
         <f t="shared" si="1"/>
-        <v>620</v>
+        <v>610</v>
       </c>
       <c r="K11" s="14" t="s">
         <v>53</v>
@@ -1963,7 +1963,7 @@
         <v>300</v>
       </c>
       <c r="E12" s="12">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="F12" s="12">
         <v>0</v>
@@ -1976,11 +1976,11 @@
       </c>
       <c r="I12" s="13">
         <f t="shared" si="0"/>
-        <v>920</v>
+        <v>1040</v>
       </c>
       <c r="J12" s="13">
         <f t="shared" si="1"/>
-        <v>520</v>
+        <v>400</v>
       </c>
       <c r="K12" s="14" t="s">
         <v>53</v>
@@ -2009,7 +2009,7 @@
         <v>330</v>
       </c>
       <c r="E13" s="12">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="F13" s="12">
         <v>0</v>
@@ -2022,11 +2022,11 @@
       </c>
       <c r="I13" s="13">
         <f t="shared" si="0"/>
-        <v>950</v>
+        <v>1010</v>
       </c>
       <c r="J13" s="13">
         <f t="shared" si="1"/>
-        <v>490</v>
+        <v>430</v>
       </c>
       <c r="K13" s="14" t="s">
         <v>53</v>
@@ -2055,7 +2055,7 @@
         <v>120</v>
       </c>
       <c r="E14" s="12">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F14" s="12">
         <v>350</v>
@@ -2068,11 +2068,11 @@
       </c>
       <c r="I14" s="13">
         <f t="shared" si="0"/>
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="J14" s="13">
         <f t="shared" si="1"/>
-        <v>490</v>
+        <v>470</v>
       </c>
       <c r="K14" s="14" t="s">
         <v>53</v>
@@ -2101,7 +2101,7 @@
         <v>180</v>
       </c>
       <c r="E15" s="12">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F15" s="12">
         <v>200</v>
@@ -2114,11 +2114,11 @@
       </c>
       <c r="I15" s="13">
         <f t="shared" si="0"/>
-        <v>880</v>
+        <v>900</v>
       </c>
       <c r="J15" s="13">
         <f t="shared" si="1"/>
-        <v>560</v>
+        <v>540</v>
       </c>
       <c r="K15" s="14" t="s">
         <v>53</v>
@@ -2147,7 +2147,7 @@
         <v>180</v>
       </c>
       <c r="E16" s="12">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F16" s="12">
         <v>300</v>
@@ -2160,11 +2160,11 @@
       </c>
       <c r="I16" s="13">
         <f t="shared" si="0"/>
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="J16" s="13">
         <f t="shared" si="1"/>
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="K16" s="14" t="s">
         <v>53</v>
@@ -2193,7 +2193,7 @@
         <v>240</v>
       </c>
       <c r="E17" s="12">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F17" s="12">
         <v>200</v>
@@ -2206,11 +2206,11 @@
       </c>
       <c r="I17" s="13">
         <f t="shared" si="0"/>
-        <v>920</v>
+        <v>940</v>
       </c>
       <c r="J17" s="13">
         <f t="shared" si="1"/>
-        <v>520</v>
+        <v>500</v>
       </c>
       <c r="K17" s="14" t="s">
         <v>53</v>
@@ -2239,7 +2239,7 @@
         <v>180</v>
       </c>
       <c r="E18" s="12">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F18" s="12">
         <v>250</v>
@@ -2252,11 +2252,11 @@
       </c>
       <c r="I18" s="13">
         <f t="shared" si="0"/>
-        <v>910</v>
+        <v>940</v>
       </c>
       <c r="J18" s="13">
         <f t="shared" si="1"/>
-        <v>530</v>
+        <v>500</v>
       </c>
       <c r="K18" s="14" t="s">
         <v>53</v>
@@ -2285,7 +2285,7 @@
         <v>200</v>
       </c>
       <c r="E19" s="12">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="F19" s="12">
         <v>0</v>
@@ -2298,11 +2298,11 @@
       </c>
       <c r="I19" s="13">
         <f t="shared" si="0"/>
-        <v>820</v>
+        <v>840</v>
       </c>
       <c r="J19" s="13">
         <f t="shared" si="1"/>
-        <v>620</v>
+        <v>600</v>
       </c>
       <c r="K19" s="14" t="s">
         <v>53</v>
@@ -2331,7 +2331,7 @@
         <v>330</v>
       </c>
       <c r="E20" s="12">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="F20" s="12">
         <v>0</v>
@@ -2344,11 +2344,11 @@
       </c>
       <c r="I20" s="13">
         <f t="shared" si="0"/>
-        <v>1010</v>
+        <v>950</v>
       </c>
       <c r="J20" s="13">
         <f t="shared" si="1"/>
-        <v>430</v>
+        <v>490</v>
       </c>
       <c r="K20" s="14" t="s">
         <v>53</v>
@@ -2377,7 +2377,7 @@
         <v>180</v>
       </c>
       <c r="E21" s="12">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F21" s="12">
         <v>300</v>
@@ -2390,11 +2390,11 @@
       </c>
       <c r="I21" s="13">
         <f t="shared" si="0"/>
-        <v>960</v>
+        <v>990</v>
       </c>
       <c r="J21" s="13">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>450</v>
       </c>
       <c r="K21" s="14" t="s">
         <v>53</v>
@@ -2423,7 +2423,7 @@
         <v>120</v>
       </c>
       <c r="E22" s="12">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F22" s="12">
         <v>300</v>
@@ -2436,11 +2436,11 @@
       </c>
       <c r="I22" s="13">
         <f t="shared" si="0"/>
-        <v>890</v>
+        <v>920</v>
       </c>
       <c r="J22" s="13">
         <f t="shared" si="1"/>
-        <v>550</v>
+        <v>520</v>
       </c>
       <c r="K22" s="14" t="s">
         <v>53</v>
@@ -2469,7 +2469,7 @@
         <v>180</v>
       </c>
       <c r="E23" s="12">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="F23" s="12">
         <v>300</v>
@@ -2482,11 +2482,11 @@
       </c>
       <c r="I23" s="13">
         <f t="shared" si="0"/>
-        <v>955</v>
+        <v>980</v>
       </c>
       <c r="J23" s="13">
         <f t="shared" si="1"/>
-        <v>485</v>
+        <v>460</v>
       </c>
       <c r="K23" s="14" t="s">
         <v>53</v>
@@ -2515,7 +2515,7 @@
         <v>240</v>
       </c>
       <c r="E24" s="12">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F24" s="12">
         <v>200</v>
@@ -2528,11 +2528,11 @@
       </c>
       <c r="I24" s="13">
         <f t="shared" si="0"/>
-        <v>930</v>
+        <v>950</v>
       </c>
       <c r="J24" s="13">
         <f t="shared" si="1"/>
-        <v>510</v>
+        <v>490</v>
       </c>
       <c r="K24" s="14" t="s">
         <v>53</v>
@@ -2607,7 +2607,7 @@
         <v>300</v>
       </c>
       <c r="E26" s="12">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="F26" s="12">
         <v>0</v>
@@ -2620,11 +2620,11 @@
       </c>
       <c r="I26" s="13">
         <f t="shared" si="0"/>
-        <v>920</v>
+        <v>990</v>
       </c>
       <c r="J26" s="13">
         <f t="shared" si="1"/>
-        <v>520</v>
+        <v>450</v>
       </c>
       <c r="K26" s="14" t="s">
         <v>53</v>
@@ -2653,7 +2653,7 @@
         <v>330</v>
       </c>
       <c r="E27" s="12">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="F27" s="12">
         <v>0</v>
@@ -2666,11 +2666,11 @@
       </c>
       <c r="I27" s="13">
         <f t="shared" si="0"/>
-        <v>920</v>
+        <v>1020</v>
       </c>
       <c r="J27" s="13">
         <f t="shared" si="1"/>
-        <v>520</v>
+        <v>420</v>
       </c>
       <c r="K27" s="14" t="s">
         <v>53</v>
@@ -2699,7 +2699,7 @@
         <v>180</v>
       </c>
       <c r="E28" s="12">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F28" s="12">
         <v>300</v>
@@ -2712,11 +2712,11 @@
       </c>
       <c r="I28" s="13">
         <f t="shared" si="0"/>
-        <v>960</v>
+        <v>990</v>
       </c>
       <c r="J28" s="13">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>450</v>
       </c>
       <c r="K28" s="14" t="s">
         <v>53</v>
@@ -2740,14 +2740,8 @@
       <c r="F29" s="12"/>
       <c r="G29" s="12"/>
       <c r="H29" s="12"/>
-      <c r="I29" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I29" s="13"/>
+      <c r="J29" s="13"/>
       <c r="K29" s="14"/>
       <c r="L29" s="14"/>
       <c r="M29" s="14"/>
@@ -2762,14 +2756,8 @@
       <c r="F30" s="12"/>
       <c r="G30" s="12"/>
       <c r="H30" s="12"/>
-      <c r="I30" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I30" s="13"/>
+      <c r="J30" s="13"/>
       <c r="K30" s="14"/>
       <c r="L30" s="14"/>
       <c r="M30" s="14"/>
@@ -2784,14 +2772,8 @@
       <c r="F31" s="12"/>
       <c r="G31" s="12"/>
       <c r="H31" s="12"/>
-      <c r="I31" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I31" s="13"/>
+      <c r="J31" s="13"/>
       <c r="K31" s="14"/>
       <c r="L31" s="14"/>
       <c r="M31" s="14"/>
@@ -2806,14 +2788,8 @@
       <c r="F32" s="12"/>
       <c r="G32" s="12"/>
       <c r="H32" s="12"/>
-      <c r="I32" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I32" s="13"/>
+      <c r="J32" s="13"/>
       <c r="K32" s="14"/>
       <c r="L32" s="14"/>
       <c r="M32" s="14"/>
@@ -2828,14 +2804,8 @@
       <c r="F33" s="12"/>
       <c r="G33" s="12"/>
       <c r="H33" s="12"/>
-      <c r="I33" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I33" s="13"/>
+      <c r="J33" s="13"/>
       <c r="K33" s="14"/>
       <c r="L33" s="14"/>
       <c r="M33" s="14"/>
@@ -2850,14 +2820,8 @@
       <c r="F34" s="12"/>
       <c r="G34" s="12"/>
       <c r="H34" s="12"/>
-      <c r="I34" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I34" s="13"/>
+      <c r="J34" s="13"/>
       <c r="K34" s="14"/>
       <c r="L34" s="14"/>
       <c r="M34" s="14"/>
@@ -2872,14 +2836,8 @@
       <c r="F35" s="12"/>
       <c r="G35" s="12"/>
       <c r="H35" s="12"/>
-      <c r="I35" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I35" s="13"/>
+      <c r="J35" s="13"/>
       <c r="K35" s="14"/>
       <c r="L35" s="14"/>
       <c r="M35" s="14"/>
@@ -2894,14 +2852,8 @@
       <c r="F36" s="12"/>
       <c r="G36" s="12"/>
       <c r="H36" s="12"/>
-      <c r="I36" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I36" s="13"/>
+      <c r="J36" s="13"/>
       <c r="K36" s="14"/>
       <c r="L36" s="14"/>
       <c r="M36" s="14"/>
@@ -2916,14 +2868,8 @@
       <c r="F37" s="12"/>
       <c r="G37" s="12"/>
       <c r="H37" s="12"/>
-      <c r="I37" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I37" s="13"/>
+      <c r="J37" s="13"/>
       <c r="K37" s="14"/>
       <c r="L37" s="14"/>
       <c r="M37" s="14"/>
@@ -2938,14 +2884,8 @@
       <c r="F38" s="12"/>
       <c r="G38" s="12"/>
       <c r="H38" s="12"/>
-      <c r="I38" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I38" s="13"/>
+      <c r="J38" s="13"/>
       <c r="K38" s="14"/>
       <c r="L38" s="14"/>
       <c r="M38" s="14"/>
@@ -2960,14 +2900,8 @@
       <c r="F39" s="12"/>
       <c r="G39" s="12"/>
       <c r="H39" s="12"/>
-      <c r="I39" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I39" s="13"/>
+      <c r="J39" s="13"/>
       <c r="K39" s="14"/>
       <c r="L39" s="14"/>
       <c r="M39" s="14"/>
@@ -2982,14 +2916,8 @@
       <c r="F40" s="12"/>
       <c r="G40" s="12"/>
       <c r="H40" s="12"/>
-      <c r="I40" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I40" s="13"/>
+      <c r="J40" s="13"/>
       <c r="K40" s="14"/>
       <c r="L40" s="14"/>
       <c r="M40" s="14"/>
@@ -3004,14 +2932,8 @@
       <c r="F41" s="12"/>
       <c r="G41" s="12"/>
       <c r="H41" s="12"/>
-      <c r="I41" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I41" s="13"/>
+      <c r="J41" s="13"/>
       <c r="K41" s="14"/>
       <c r="L41" s="14"/>
       <c r="M41" s="14"/>
@@ -3026,14 +2948,8 @@
       <c r="F42" s="12"/>
       <c r="G42" s="12"/>
       <c r="H42" s="12"/>
-      <c r="I42" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I42" s="13"/>
+      <c r="J42" s="13"/>
       <c r="K42" s="14"/>
       <c r="L42" s="14"/>
       <c r="M42" s="14"/>
@@ -3048,14 +2964,8 @@
       <c r="F43" s="12"/>
       <c r="G43" s="12"/>
       <c r="H43" s="12"/>
-      <c r="I43" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I43" s="13"/>
+      <c r="J43" s="13"/>
       <c r="K43" s="14"/>
       <c r="L43" s="14"/>
       <c r="M43" s="14"/>
@@ -3070,14 +2980,8 @@
       <c r="F44" s="12"/>
       <c r="G44" s="12"/>
       <c r="H44" s="12"/>
-      <c r="I44" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I44" s="13"/>
+      <c r="J44" s="13"/>
       <c r="K44" s="14"/>
       <c r="L44" s="14"/>
       <c r="M44" s="14"/>

--- a/12623065.xlsx
+++ b/12623065.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="98">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -265,6 +265,63 @@
   </si>
   <si>
     <t>Good use of time.</t>
+  </si>
+  <si>
+    <t>Felt satisfied with my progress.</t>
+  </si>
+  <si>
+    <t>completed my classes and stayed on schedule.</t>
+  </si>
+  <si>
+    <t>Good day with regular classes.</t>
+  </si>
+  <si>
+    <t>Had a good day and manage my time well.</t>
+  </si>
+  <si>
+    <t>Started the week with a focused.</t>
+  </si>
+  <si>
+    <t>Attend all classes.</t>
+  </si>
+  <si>
+    <t>Made good use of my time.</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Fresher's party is organized today.Enjoying with friends but feeling low .</t>
+  </si>
+  <si>
+    <t>Ending the day with satisfaction.</t>
+  </si>
+  <si>
+    <t>Relaxing and preparing for upcoming week.</t>
+  </si>
+  <si>
+    <t>Focusing more on studies.</t>
+  </si>
+  <si>
+    <t>Keeping myself motivated.</t>
+  </si>
+  <si>
+    <t>Mainting the schedule.</t>
+  </si>
+  <si>
+    <t>Feeling a little tired.</t>
+  </si>
+  <si>
+    <t>Working hard on my work.</t>
+  </si>
+  <si>
+    <t>Preparing for CA.</t>
+  </si>
+  <si>
+    <t>Today I had my CA , and it went very well.So feeling good.</t>
   </si>
 </sst>
 </file>
@@ -985,7 +1042,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1022,6 +1079,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1359,181 +1431,181 @@
   </cols>
   <sheetData>
     <row r="1" ht="23.25" spans="1:1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:1">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="19"/>
+      <c r="A4" s="24"/>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="25" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="24" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="19"/>
+      <c r="A7" s="24"/>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="25" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="24" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="24" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="24" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="19"/>
+      <c r="A12" s="24"/>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="25" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="24" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="24" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="19"/>
+      <c r="A16" s="24"/>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="20" t="s">
+      <c r="A17" s="25" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="24" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="19" t="s">
+      <c r="A19" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="19" t="s">
+      <c r="A20" s="24" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="19" t="s">
+      <c r="A21" s="24" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="19" t="s">
+      <c r="A22" s="24" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="19" t="s">
+      <c r="A23" s="24" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="19" t="s">
+      <c r="A24" s="24" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="19" t="s">
+      <c r="A25" s="24" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="19" t="s">
+      <c r="A26" s="24" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="19" t="s">
+      <c r="A27" s="24" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="19" t="s">
+      <c r="A28" s="24" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="19" t="s">
+      <c r="A29" s="24" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="19" t="s">
+      <c r="A30" s="24" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="19" t="s">
+      <c r="A31" s="24" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="19"/>
+      <c r="A32" s="24"/>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="20" t="s">
+      <c r="A33" s="25" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="19" t="s">
+      <c r="A34" s="24" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="19" t="s">
+      <c r="A35" s="24" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="19"/>
+      <c r="A36" s="24"/>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="20"/>
+      <c r="A37" s="25"/>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="19"/>
+      <c r="A38" s="24"/>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="19"/>
+      <c r="A39" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2731,327 +2803,877 @@
         <v>64</v>
       </c>
     </row>
-    <row r="29" spans="1:14">
-      <c r="A29" s="11"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="13"/>
-      <c r="K29" s="14"/>
-      <c r="L29" s="14"/>
-      <c r="M29" s="14"/>
-      <c r="N29" s="15"/>
-    </row>
-    <row r="30" spans="1:14">
-      <c r="A30" s="11"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="13"/>
-      <c r="K30" s="14"/>
-      <c r="L30" s="14"/>
-      <c r="M30" s="14"/>
-      <c r="N30" s="15"/>
+    <row r="29" ht="30" spans="1:14">
+      <c r="A29" s="16">
+        <v>46266</v>
+      </c>
+      <c r="B29" s="17">
+        <v>420</v>
+      </c>
+      <c r="C29" s="17">
+        <v>20</v>
+      </c>
+      <c r="D29" s="17">
+        <v>120</v>
+      </c>
+      <c r="E29" s="17">
+        <v>40</v>
+      </c>
+      <c r="F29" s="17">
+        <v>300</v>
+      </c>
+      <c r="G29" s="17">
+        <v>6</v>
+      </c>
+      <c r="H29" s="17">
+        <v>30</v>
+      </c>
+      <c r="I29" s="18">
+        <f t="shared" si="0"/>
+        <v>930</v>
+      </c>
+      <c r="J29" s="18">
+        <f t="shared" si="1"/>
+        <v>510</v>
+      </c>
+      <c r="K29" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="L29" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="M29" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="N29" s="20" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="30" ht="30" spans="1:14">
+      <c r="A30" s="16">
+        <v>46267</v>
+      </c>
+      <c r="B30" s="17">
+        <v>420</v>
+      </c>
+      <c r="C30" s="17">
+        <v>20</v>
+      </c>
+      <c r="D30" s="17">
+        <v>180</v>
+      </c>
+      <c r="E30" s="17">
+        <v>40</v>
+      </c>
+      <c r="F30" s="17">
+        <v>300</v>
+      </c>
+      <c r="G30" s="17">
+        <v>6</v>
+      </c>
+      <c r="H30" s="17">
+        <v>30</v>
+      </c>
+      <c r="I30" s="18">
+        <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+      <c r="J30" s="18">
+        <f t="shared" si="1"/>
+        <v>450</v>
+      </c>
+      <c r="K30" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="L30" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="M30" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="N30" s="20" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="31" spans="1:14">
-      <c r="A31" s="11"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="13"/>
-      <c r="J31" s="13"/>
-      <c r="K31" s="14"/>
-      <c r="L31" s="14"/>
-      <c r="M31" s="14"/>
-      <c r="N31" s="15"/>
+      <c r="A31" s="16">
+        <v>46268</v>
+      </c>
+      <c r="B31" s="17">
+        <v>420</v>
+      </c>
+      <c r="C31" s="17">
+        <v>20</v>
+      </c>
+      <c r="D31" s="17">
+        <v>180</v>
+      </c>
+      <c r="E31" s="17">
+        <v>40</v>
+      </c>
+      <c r="F31" s="17">
+        <v>200</v>
+      </c>
+      <c r="G31" s="17">
+        <v>4</v>
+      </c>
+      <c r="H31" s="17">
+        <v>50</v>
+      </c>
+      <c r="I31" s="18">
+        <f t="shared" si="0"/>
+        <v>910</v>
+      </c>
+      <c r="J31" s="18">
+        <f t="shared" si="1"/>
+        <v>530</v>
+      </c>
+      <c r="K31" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="L31" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="M31" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="N31" s="20" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="32" spans="1:14">
-      <c r="A32" s="11"/>
-      <c r="B32" s="12"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="12"/>
-      <c r="I32" s="13"/>
-      <c r="J32" s="13"/>
-      <c r="K32" s="14"/>
-      <c r="L32" s="14"/>
-      <c r="M32" s="14"/>
-      <c r="N32" s="15"/>
+      <c r="A32" s="16">
+        <v>46269</v>
+      </c>
+      <c r="B32" s="17">
+        <v>420</v>
+      </c>
+      <c r="C32" s="17">
+        <v>20</v>
+      </c>
+      <c r="D32" s="17">
+        <v>180</v>
+      </c>
+      <c r="E32" s="17">
+        <v>30</v>
+      </c>
+      <c r="F32" s="17">
+        <v>250</v>
+      </c>
+      <c r="G32" s="17">
+        <v>5</v>
+      </c>
+      <c r="H32" s="17">
+        <v>40</v>
+      </c>
+      <c r="I32" s="18">
+        <f t="shared" si="0"/>
+        <v>940</v>
+      </c>
+      <c r="J32" s="18">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="K32" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="L32" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="M32" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="N32" s="20"/>
     </row>
     <row r="33" spans="1:14">
-      <c r="A33" s="11"/>
-      <c r="B33" s="12"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="13"/>
-      <c r="J33" s="13"/>
-      <c r="K33" s="14"/>
-      <c r="L33" s="14"/>
-      <c r="M33" s="14"/>
-      <c r="N33" s="15"/>
-    </row>
-    <row r="34" spans="1:14">
-      <c r="A34" s="11"/>
-      <c r="B34" s="12"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="12"/>
-      <c r="I34" s="13"/>
-      <c r="J34" s="13"/>
-      <c r="K34" s="14"/>
-      <c r="L34" s="14"/>
-      <c r="M34" s="14"/>
-      <c r="N34" s="15"/>
-    </row>
-    <row r="35" spans="1:14">
-      <c r="A35" s="11"/>
-      <c r="B35" s="12"/>
-      <c r="C35" s="12"/>
-      <c r="D35" s="12"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="12"/>
-      <c r="H35" s="12"/>
-      <c r="I35" s="13"/>
-      <c r="J35" s="13"/>
-      <c r="K35" s="14"/>
-      <c r="L35" s="14"/>
-      <c r="M35" s="14"/>
-      <c r="N35" s="15"/>
+      <c r="A33" s="16">
+        <v>46270</v>
+      </c>
+      <c r="B33" s="17">
+        <v>480</v>
+      </c>
+      <c r="C33" s="17">
+        <v>40</v>
+      </c>
+      <c r="D33" s="17">
+        <v>360</v>
+      </c>
+      <c r="E33" s="17">
+        <v>180</v>
+      </c>
+      <c r="F33" s="17">
+        <v>0</v>
+      </c>
+      <c r="G33" s="17">
+        <v>0</v>
+      </c>
+      <c r="H33" s="17">
+        <v>120</v>
+      </c>
+      <c r="I33" s="18">
+        <f t="shared" si="0"/>
+        <v>1180</v>
+      </c>
+      <c r="J33" s="18">
+        <f t="shared" si="1"/>
+        <v>260</v>
+      </c>
+      <c r="K33" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="L33" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="M33" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="N33" s="20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="34" ht="30" spans="1:14">
+      <c r="A34" s="16">
+        <v>46271</v>
+      </c>
+      <c r="B34" s="17">
+        <v>480</v>
+      </c>
+      <c r="C34" s="17">
+        <v>60</v>
+      </c>
+      <c r="D34" s="17">
+        <v>240</v>
+      </c>
+      <c r="E34" s="17">
+        <v>120</v>
+      </c>
+      <c r="F34" s="17">
+        <v>0</v>
+      </c>
+      <c r="G34" s="17">
+        <v>0</v>
+      </c>
+      <c r="H34" s="17">
+        <v>50</v>
+      </c>
+      <c r="I34" s="18">
+        <f t="shared" si="0"/>
+        <v>950</v>
+      </c>
+      <c r="J34" s="18">
+        <f t="shared" si="1"/>
+        <v>490</v>
+      </c>
+      <c r="K34" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="L34" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="M34" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="N34" s="20" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="35" ht="30" spans="1:14">
+      <c r="A35" s="16">
+        <v>46272</v>
+      </c>
+      <c r="B35" s="17">
+        <v>420</v>
+      </c>
+      <c r="C35" s="17">
+        <v>20</v>
+      </c>
+      <c r="D35" s="17">
+        <v>120</v>
+      </c>
+      <c r="E35" s="17">
+        <v>40</v>
+      </c>
+      <c r="F35" s="17">
+        <v>300</v>
+      </c>
+      <c r="G35" s="17">
+        <v>6</v>
+      </c>
+      <c r="H35" s="17">
+        <v>30</v>
+      </c>
+      <c r="I35" s="18">
+        <f t="shared" si="0"/>
+        <v>930</v>
+      </c>
+      <c r="J35" s="18">
+        <f t="shared" si="1"/>
+        <v>510</v>
+      </c>
+      <c r="K35" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="L35" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="M35" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="N35" s="20" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="36" spans="1:14">
-      <c r="A36" s="11"/>
-      <c r="B36" s="12"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="12"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="12"/>
-      <c r="H36" s="12"/>
-      <c r="I36" s="13"/>
-      <c r="J36" s="13"/>
-      <c r="K36" s="14"/>
-      <c r="L36" s="14"/>
-      <c r="M36" s="14"/>
-      <c r="N36" s="15"/>
+      <c r="A36" s="16">
+        <v>46273</v>
+      </c>
+      <c r="B36" s="17">
+        <v>420</v>
+      </c>
+      <c r="C36" s="17">
+        <v>20</v>
+      </c>
+      <c r="D36" s="17">
+        <v>120</v>
+      </c>
+      <c r="E36" s="17">
+        <v>40</v>
+      </c>
+      <c r="F36" s="17">
+        <v>300</v>
+      </c>
+      <c r="G36" s="17">
+        <v>6</v>
+      </c>
+      <c r="H36" s="17">
+        <v>20</v>
+      </c>
+      <c r="I36" s="18">
+        <f t="shared" si="0"/>
+        <v>920</v>
+      </c>
+      <c r="J36" s="18">
+        <f t="shared" si="1"/>
+        <v>520</v>
+      </c>
+      <c r="K36" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="L36" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="M36" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="N36" s="20" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="37" spans="1:14">
-      <c r="A37" s="11"/>
-      <c r="B37" s="12"/>
-      <c r="C37" s="12"/>
-      <c r="D37" s="12"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="12"/>
-      <c r="G37" s="12"/>
-      <c r="H37" s="12"/>
-      <c r="I37" s="13"/>
-      <c r="J37" s="13"/>
-      <c r="K37" s="14"/>
-      <c r="L37" s="14"/>
-      <c r="M37" s="14"/>
-      <c r="N37" s="15"/>
-    </row>
-    <row r="38" spans="1:14">
-      <c r="A38" s="11"/>
-      <c r="B38" s="12"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="12"/>
-      <c r="E38" s="12"/>
-      <c r="F38" s="12"/>
-      <c r="G38" s="12"/>
-      <c r="H38" s="12"/>
-      <c r="I38" s="13"/>
-      <c r="J38" s="13"/>
-      <c r="K38" s="14"/>
-      <c r="L38" s="14"/>
-      <c r="M38" s="14"/>
-      <c r="N38" s="15"/>
-    </row>
-    <row r="39" spans="1:14">
-      <c r="A39" s="11"/>
-      <c r="B39" s="12"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="12"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
-      <c r="G39" s="12"/>
-      <c r="H39" s="12"/>
-      <c r="I39" s="13"/>
-      <c r="J39" s="13"/>
-      <c r="K39" s="14"/>
-      <c r="L39" s="14"/>
-      <c r="M39" s="14"/>
-      <c r="N39" s="15"/>
-    </row>
-    <row r="40" spans="1:14">
-      <c r="A40" s="11"/>
-      <c r="B40" s="12"/>
-      <c r="C40" s="12"/>
-      <c r="D40" s="12"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="12"/>
-      <c r="G40" s="12"/>
-      <c r="H40" s="12"/>
-      <c r="I40" s="13"/>
-      <c r="J40" s="13"/>
-      <c r="K40" s="14"/>
-      <c r="L40" s="14"/>
-      <c r="M40" s="14"/>
-      <c r="N40" s="15"/>
+      <c r="A37" s="16">
+        <v>46274</v>
+      </c>
+      <c r="B37" s="17">
+        <v>420</v>
+      </c>
+      <c r="C37" s="17">
+        <v>20</v>
+      </c>
+      <c r="D37" s="17">
+        <v>180</v>
+      </c>
+      <c r="E37" s="17">
+        <v>50</v>
+      </c>
+      <c r="F37" s="17">
+        <v>300</v>
+      </c>
+      <c r="G37" s="17">
+        <v>6</v>
+      </c>
+      <c r="H37" s="17">
+        <v>20</v>
+      </c>
+      <c r="I37" s="18">
+        <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+      <c r="J37" s="18">
+        <f t="shared" si="1"/>
+        <v>450</v>
+      </c>
+      <c r="K37" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="L37" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="M37" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="N37" s="20" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="38" ht="45" spans="1:14">
+      <c r="A38" s="16">
+        <v>46275</v>
+      </c>
+      <c r="B38" s="17">
+        <v>420</v>
+      </c>
+      <c r="C38" s="17">
+        <v>30</v>
+      </c>
+      <c r="D38" s="17">
+        <v>60</v>
+      </c>
+      <c r="E38" s="17">
+        <v>20</v>
+      </c>
+      <c r="F38" s="17">
+        <v>100</v>
+      </c>
+      <c r="G38" s="17">
+        <v>2</v>
+      </c>
+      <c r="H38" s="17">
+        <v>180</v>
+      </c>
+      <c r="I38" s="18">
+        <f t="shared" si="0"/>
+        <v>810</v>
+      </c>
+      <c r="J38" s="18">
+        <f t="shared" si="1"/>
+        <v>630</v>
+      </c>
+      <c r="K38" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="L38" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="M38" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="N38" s="20" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="39" ht="30" spans="1:14">
+      <c r="A39" s="16">
+        <v>46276</v>
+      </c>
+      <c r="B39" s="17">
+        <v>420</v>
+      </c>
+      <c r="C39" s="17">
+        <v>30</v>
+      </c>
+      <c r="D39" s="17">
+        <v>120</v>
+      </c>
+      <c r="E39" s="17">
+        <v>60</v>
+      </c>
+      <c r="F39" s="17">
+        <v>250</v>
+      </c>
+      <c r="G39" s="17">
+        <v>5</v>
+      </c>
+      <c r="H39" s="17">
+        <v>30</v>
+      </c>
+      <c r="I39" s="18">
+        <f t="shared" si="0"/>
+        <v>910</v>
+      </c>
+      <c r="J39" s="18">
+        <f t="shared" si="1"/>
+        <v>530</v>
+      </c>
+      <c r="K39" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="L39" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="M39" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="N39" s="20" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="40" ht="30" spans="1:14">
+      <c r="A40" s="16">
+        <v>46277</v>
+      </c>
+      <c r="B40" s="17">
+        <v>480</v>
+      </c>
+      <c r="C40" s="17">
+        <v>30</v>
+      </c>
+      <c r="D40" s="17">
+        <v>240</v>
+      </c>
+      <c r="E40" s="17">
+        <v>60</v>
+      </c>
+      <c r="F40" s="17">
+        <v>0</v>
+      </c>
+      <c r="G40" s="17">
+        <v>0</v>
+      </c>
+      <c r="H40" s="17">
+        <v>60</v>
+      </c>
+      <c r="I40" s="18">
+        <f t="shared" si="0"/>
+        <v>870</v>
+      </c>
+      <c r="J40" s="18">
+        <f t="shared" si="1"/>
+        <v>570</v>
+      </c>
+      <c r="K40" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="L40" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="M40" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="N40" s="20" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="41" spans="1:14">
-      <c r="A41" s="11"/>
-      <c r="B41" s="12"/>
-      <c r="C41" s="12"/>
-      <c r="D41" s="12"/>
-      <c r="E41" s="12"/>
-      <c r="F41" s="12"/>
-      <c r="G41" s="12"/>
-      <c r="H41" s="12"/>
-      <c r="I41" s="13"/>
-      <c r="J41" s="13"/>
-      <c r="K41" s="14"/>
-      <c r="L41" s="14"/>
-      <c r="M41" s="14"/>
-      <c r="N41" s="15"/>
+      <c r="A41" s="16">
+        <v>46278</v>
+      </c>
+      <c r="B41" s="17">
+        <v>480</v>
+      </c>
+      <c r="C41" s="17">
+        <v>40</v>
+      </c>
+      <c r="D41" s="17">
+        <v>360</v>
+      </c>
+      <c r="E41" s="17">
+        <v>50</v>
+      </c>
+      <c r="F41" s="17">
+        <v>0</v>
+      </c>
+      <c r="G41" s="17">
+        <v>0</v>
+      </c>
+      <c r="H41" s="17">
+        <v>90</v>
+      </c>
+      <c r="I41" s="18">
+        <f t="shared" si="0"/>
+        <v>1020</v>
+      </c>
+      <c r="J41" s="18">
+        <f t="shared" si="1"/>
+        <v>420</v>
+      </c>
+      <c r="K41" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="L41" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="M41" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="N41" s="20" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="42" spans="1:14">
-      <c r="A42" s="11"/>
-      <c r="B42" s="12"/>
-      <c r="C42" s="12"/>
-      <c r="D42" s="12"/>
-      <c r="E42" s="12"/>
-      <c r="F42" s="12"/>
-      <c r="G42" s="12"/>
-      <c r="H42" s="12"/>
-      <c r="I42" s="13"/>
-      <c r="J42" s="13"/>
-      <c r="K42" s="14"/>
-      <c r="L42" s="14"/>
-      <c r="M42" s="14"/>
-      <c r="N42" s="15"/>
+      <c r="A42" s="16">
+        <v>46279</v>
+      </c>
+      <c r="B42" s="17">
+        <v>420</v>
+      </c>
+      <c r="C42" s="17">
+        <v>20</v>
+      </c>
+      <c r="D42" s="17">
+        <v>180</v>
+      </c>
+      <c r="E42" s="17">
+        <v>40</v>
+      </c>
+      <c r="F42" s="17">
+        <v>300</v>
+      </c>
+      <c r="G42" s="17">
+        <v>6</v>
+      </c>
+      <c r="H42" s="17">
+        <v>150</v>
+      </c>
+      <c r="I42" s="18">
+        <f t="shared" si="0"/>
+        <v>1110</v>
+      </c>
+      <c r="J42" s="18">
+        <f t="shared" si="1"/>
+        <v>330</v>
+      </c>
+      <c r="K42" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="L42" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="M42" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="N42" s="20" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="43" spans="1:14">
-      <c r="A43" s="11"/>
-      <c r="B43" s="12"/>
-      <c r="C43" s="12"/>
-      <c r="D43" s="12"/>
-      <c r="E43" s="12"/>
-      <c r="F43" s="12"/>
-      <c r="G43" s="12"/>
-      <c r="H43" s="12"/>
-      <c r="I43" s="13"/>
-      <c r="J43" s="13"/>
-      <c r="K43" s="14"/>
-      <c r="L43" s="14"/>
-      <c r="M43" s="14"/>
-      <c r="N43" s="15"/>
+      <c r="A43" s="16">
+        <v>46280</v>
+      </c>
+      <c r="B43" s="17">
+        <v>420</v>
+      </c>
+      <c r="C43" s="17">
+        <v>20</v>
+      </c>
+      <c r="D43" s="17">
+        <v>180</v>
+      </c>
+      <c r="E43" s="17">
+        <v>30</v>
+      </c>
+      <c r="F43" s="17">
+        <v>300</v>
+      </c>
+      <c r="G43" s="17">
+        <v>6</v>
+      </c>
+      <c r="H43" s="17">
+        <v>30</v>
+      </c>
+      <c r="I43" s="18">
+        <f t="shared" si="0"/>
+        <v>980</v>
+      </c>
+      <c r="J43" s="18">
+        <f t="shared" si="1"/>
+        <v>460</v>
+      </c>
+      <c r="K43" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="L43" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="M43" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="N43" s="20" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="44" spans="1:14">
-      <c r="A44" s="11"/>
-      <c r="B44" s="12"/>
-      <c r="C44" s="12"/>
-      <c r="D44" s="12"/>
-      <c r="E44" s="12"/>
-      <c r="F44" s="12"/>
-      <c r="G44" s="12"/>
-      <c r="H44" s="12"/>
-      <c r="I44" s="13"/>
-      <c r="J44" s="13"/>
-      <c r="K44" s="14"/>
-      <c r="L44" s="14"/>
-      <c r="M44" s="14"/>
-      <c r="N44" s="15"/>
+      <c r="A44" s="16">
+        <v>46281</v>
+      </c>
+      <c r="B44" s="17">
+        <v>420</v>
+      </c>
+      <c r="C44" s="17">
+        <v>20</v>
+      </c>
+      <c r="D44" s="17">
+        <v>180</v>
+      </c>
+      <c r="E44" s="17">
+        <v>40</v>
+      </c>
+      <c r="F44" s="17">
+        <v>300</v>
+      </c>
+      <c r="G44" s="17">
+        <v>6</v>
+      </c>
+      <c r="H44" s="17">
+        <v>20</v>
+      </c>
+      <c r="I44" s="18">
+        <f t="shared" si="0"/>
+        <v>980</v>
+      </c>
+      <c r="J44" s="18">
+        <f t="shared" si="1"/>
+        <v>460</v>
+      </c>
+      <c r="K44" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="L44" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="M44" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="N44" s="20" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="45" spans="1:14">
-      <c r="A45" s="11"/>
-      <c r="B45" s="12"/>
-      <c r="C45" s="12"/>
-      <c r="D45" s="12"/>
-      <c r="E45" s="12"/>
-      <c r="F45" s="12"/>
-      <c r="G45" s="12"/>
-      <c r="H45" s="12"/>
-      <c r="I45" s="13" t="str">
+      <c r="A45" s="11">
+        <v>46282</v>
+      </c>
+      <c r="B45" s="12">
+        <v>420</v>
+      </c>
+      <c r="C45" s="12">
+        <v>20</v>
+      </c>
+      <c r="D45" s="12">
+        <v>180</v>
+      </c>
+      <c r="E45" s="12">
+        <v>60</v>
+      </c>
+      <c r="F45" s="12">
+        <v>200</v>
+      </c>
+      <c r="G45" s="12">
+        <v>4</v>
+      </c>
+      <c r="H45" s="12">
+        <v>30</v>
+      </c>
+      <c r="I45" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="13" t="str">
+        <v>910</v>
+      </c>
+      <c r="J45" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="14"/>
-      <c r="L45" s="14"/>
-      <c r="M45" s="14"/>
-      <c r="N45" s="15"/>
+        <v>530</v>
+      </c>
+      <c r="K45" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L45" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M45" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N45" s="15" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="46" spans="1:14">
-      <c r="A46" s="11"/>
-      <c r="B46" s="12"/>
-      <c r="C46" s="12"/>
-      <c r="D46" s="12"/>
-      <c r="E46" s="12"/>
-      <c r="F46" s="12"/>
-      <c r="G46" s="12"/>
-      <c r="H46" s="12"/>
-      <c r="I46" s="13" t="str">
+      <c r="A46" s="11">
+        <v>46283</v>
+      </c>
+      <c r="B46" s="12">
+        <v>420</v>
+      </c>
+      <c r="C46" s="12">
+        <v>20</v>
+      </c>
+      <c r="D46" s="12">
+        <v>240</v>
+      </c>
+      <c r="E46" s="12">
+        <v>30</v>
+      </c>
+      <c r="F46" s="12">
+        <v>250</v>
+      </c>
+      <c r="G46" s="12">
+        <v>5</v>
+      </c>
+      <c r="H46" s="12">
+        <v>20</v>
+      </c>
+      <c r="I46" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="13" t="str">
+        <v>980</v>
+      </c>
+      <c r="J46" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="14"/>
-      <c r="L46" s="14"/>
-      <c r="M46" s="14"/>
-      <c r="N46" s="15"/>
-    </row>
-    <row r="47" spans="1:14">
-      <c r="A47" s="11"/>
-      <c r="B47" s="12"/>
-      <c r="C47" s="12"/>
-      <c r="D47" s="12"/>
-      <c r="E47" s="12"/>
-      <c r="F47" s="12"/>
-      <c r="G47" s="12"/>
-      <c r="H47" s="12"/>
-      <c r="I47" s="13" t="str">
+        <v>460</v>
+      </c>
+      <c r="K46" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L46" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M46" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N46" s="15" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="47" ht="45" spans="1:14">
+      <c r="A47" s="11">
+        <v>46284</v>
+      </c>
+      <c r="B47" s="12">
+        <v>240</v>
+      </c>
+      <c r="C47" s="12">
+        <v>10</v>
+      </c>
+      <c r="D47" s="12">
+        <v>300</v>
+      </c>
+      <c r="E47" s="12">
+        <v>120</v>
+      </c>
+      <c r="F47" s="12">
+        <v>0</v>
+      </c>
+      <c r="G47" s="12">
+        <v>0</v>
+      </c>
+      <c r="H47" s="12">
+        <v>20</v>
+      </c>
+      <c r="I47" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="13" t="str">
+        <v>690</v>
+      </c>
+      <c r="J47" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="14"/>
-      <c r="L47" s="14"/>
-      <c r="M47" s="14"/>
-      <c r="N47" s="15"/>
+        <v>750</v>
+      </c>
+      <c r="K47" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="L47" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M47" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="N47" s="15" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="11"/>
@@ -10850,19 +11472,24 @@
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="A4:N4"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J401">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
+  <conditionalFormatting sqref="J29:J44">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J6:J28 J45:J401">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K401">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K28 K29:K44 K45:K401">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L401">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L28 L29:L44 L45:L401">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M401">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M28 M29:M44 M45:M401">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
   </dataValidations>

--- a/12623065.xlsx
+++ b/12623065.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="18330" windowHeight="8085" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="99">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -322,6 +322,9 @@
   </si>
   <si>
     <t>Today I had my CA , and it went very well.So feeling good.</t>
+  </si>
+  <si>
+    <t>To much work to do.</t>
   </si>
 </sst>
 </file>
@@ -3676,26 +3679,50 @@
       </c>
     </row>
     <row r="48" spans="1:14">
-      <c r="A48" s="11"/>
-      <c r="B48" s="12"/>
-      <c r="C48" s="12"/>
-      <c r="D48" s="12"/>
-      <c r="E48" s="12"/>
-      <c r="F48" s="12"/>
-      <c r="G48" s="12"/>
-      <c r="H48" s="12"/>
-      <c r="I48" s="13" t="str">
+      <c r="A48" s="11">
+        <v>46285</v>
+      </c>
+      <c r="B48" s="12">
+        <v>360</v>
+      </c>
+      <c r="C48" s="12">
+        <v>30</v>
+      </c>
+      <c r="D48" s="12">
+        <v>240</v>
+      </c>
+      <c r="E48" s="12">
+        <v>30</v>
+      </c>
+      <c r="F48" s="12">
+        <v>0</v>
+      </c>
+      <c r="G48" s="12">
+        <v>0</v>
+      </c>
+      <c r="H48" s="12">
+        <v>60</v>
+      </c>
+      <c r="I48" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="13" t="str">
+        <v>720</v>
+      </c>
+      <c r="J48" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="14"/>
-      <c r="L48" s="14"/>
-      <c r="M48" s="14"/>
-      <c r="N48" s="15"/>
+        <v>720</v>
+      </c>
+      <c r="K48" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L48" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M48" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N48" s="15" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="49" spans="1:14">
       <c r="A49" s="11"/>
@@ -11483,13 +11510,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K28 K29:K44 K45:K401">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K401">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L28 L29:L44 L45:L401">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L401">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M28 M29:M44 M45:M401">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M401">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
   </dataValidations>

--- a/12623065.xlsx
+++ b/12623065.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18330" windowHeight="8085" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="18810" windowHeight="7500" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="100">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -325,6 +325,9 @@
   </si>
   <si>
     <t>To much work to do.</t>
+  </si>
+  <si>
+    <t>Attend a work shop today.</t>
   </si>
 </sst>
 </file>
@@ -3725,26 +3728,50 @@
       </c>
     </row>
     <row r="49" spans="1:14">
-      <c r="A49" s="11"/>
-      <c r="B49" s="12"/>
-      <c r="C49" s="12"/>
-      <c r="D49" s="12"/>
-      <c r="E49" s="12"/>
-      <c r="F49" s="12"/>
-      <c r="G49" s="12"/>
-      <c r="H49" s="12"/>
-      <c r="I49" s="13" t="str">
+      <c r="A49" s="11">
+        <v>46286</v>
+      </c>
+      <c r="B49" s="12">
+        <v>420</v>
+      </c>
+      <c r="C49" s="12">
+        <v>40</v>
+      </c>
+      <c r="D49" s="12">
+        <v>180</v>
+      </c>
+      <c r="E49" s="12">
+        <v>30</v>
+      </c>
+      <c r="F49" s="12">
+        <v>250</v>
+      </c>
+      <c r="G49" s="12">
+        <v>5</v>
+      </c>
+      <c r="H49" s="12">
+        <v>30</v>
+      </c>
+      <c r="I49" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="13" t="str">
+        <v>950</v>
+      </c>
+      <c r="J49" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="14"/>
-      <c r="L49" s="14"/>
-      <c r="M49" s="14"/>
-      <c r="N49" s="15"/>
+        <v>490</v>
+      </c>
+      <c r="K49" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L49" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="M49" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N49" s="15" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="50" spans="1:14">
       <c r="A50" s="11"/>

--- a/12623065.xlsx
+++ b/12623065.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18810" windowHeight="7500" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="101">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -328,6 +328,9 @@
   </si>
   <si>
     <t>Attend a work shop today.</t>
+  </si>
+  <si>
+    <t>Busy day.</t>
   </si>
 </sst>
 </file>
@@ -3774,26 +3777,50 @@
       </c>
     </row>
     <row r="50" spans="1:14">
-      <c r="A50" s="11"/>
-      <c r="B50" s="12"/>
-      <c r="C50" s="12"/>
-      <c r="D50" s="12"/>
-      <c r="E50" s="12"/>
-      <c r="F50" s="12"/>
-      <c r="G50" s="12"/>
-      <c r="H50" s="12"/>
-      <c r="I50" s="13" t="str">
+      <c r="A50" s="11">
+        <v>46287</v>
+      </c>
+      <c r="B50" s="12">
+        <v>420</v>
+      </c>
+      <c r="C50" s="12">
+        <v>30</v>
+      </c>
+      <c r="D50" s="12">
+        <v>300</v>
+      </c>
+      <c r="E50" s="12">
+        <v>30</v>
+      </c>
+      <c r="F50" s="12">
+        <v>250</v>
+      </c>
+      <c r="G50" s="12">
+        <v>5</v>
+      </c>
+      <c r="H50" s="12">
+        <v>30</v>
+      </c>
+      <c r="I50" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="13" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J50" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="14"/>
-      <c r="L50" s="14"/>
-      <c r="M50" s="14"/>
-      <c r="N50" s="15"/>
+        <v>380</v>
+      </c>
+      <c r="K50" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L50" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M50" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N50" s="15" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="51" spans="1:14">
       <c r="A51" s="11"/>

--- a/12623065.xlsx
+++ b/12623065.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="102">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -331,6 +331,9 @@
   </si>
   <si>
     <t>Busy day.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Today I had my CA , and it went good. Yesterday i studied almost since 2 am. </t>
   </si>
 </sst>
 </file>
@@ -3822,27 +3825,51 @@
         <v>100</v>
       </c>
     </row>
-    <row r="51" spans="1:14">
-      <c r="A51" s="11"/>
-      <c r="B51" s="12"/>
-      <c r="C51" s="12"/>
-      <c r="D51" s="12"/>
-      <c r="E51" s="12"/>
-      <c r="F51" s="12"/>
-      <c r="G51" s="12"/>
-      <c r="H51" s="12"/>
-      <c r="I51" s="13" t="str">
+    <row r="51" ht="45" spans="1:14">
+      <c r="A51" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B51" s="12">
+        <v>300</v>
+      </c>
+      <c r="C51" s="12">
+        <v>30</v>
+      </c>
+      <c r="D51" s="12">
+        <v>240</v>
+      </c>
+      <c r="E51" s="12">
+        <v>30</v>
+      </c>
+      <c r="F51" s="12">
+        <v>300</v>
+      </c>
+      <c r="G51" s="12">
+        <v>6</v>
+      </c>
+      <c r="H51" s="12">
+        <v>30</v>
+      </c>
+      <c r="I51" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="13" t="str">
+        <v>930</v>
+      </c>
+      <c r="J51" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="14"/>
-      <c r="L51" s="14"/>
-      <c r="M51" s="14"/>
-      <c r="N51" s="15"/>
+        <v>510</v>
+      </c>
+      <c r="K51" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L51" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M51" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N51" s="15" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="52" spans="1:14">
       <c r="A52" s="11"/>
@@ -11553,24 +11580,29 @@
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="A4:N4"/>
   </mergeCells>
-  <conditionalFormatting sqref="J29:J44">
+  <conditionalFormatting sqref="J51">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J6:J28 J45:J401">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
+  <conditionalFormatting sqref="J29:J44">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J6:J28 J45:J50 J52:J401">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K401">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K51 K6:K50 K52:K401">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L401">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L51 L6:L50 L52:L401">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M401">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M51 M6:M50 M52:M401">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
   </dataValidations>

--- a/12623065.xlsx
+++ b/12623065.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="103">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -334,6 +334,9 @@
   </si>
   <si>
     <t xml:space="preserve">Today I had my CA , and it went good. Yesterday i studied almost since 2 am. </t>
+  </si>
+  <si>
+    <t>Feeling tired because of headache.</t>
   </si>
 </sst>
 </file>
@@ -3871,27 +3874,51 @@
         <v>101</v>
       </c>
     </row>
-    <row r="52" spans="1:14">
-      <c r="A52" s="11"/>
-      <c r="B52" s="12"/>
-      <c r="C52" s="12"/>
-      <c r="D52" s="12"/>
-      <c r="E52" s="12"/>
-      <c r="F52" s="12"/>
-      <c r="G52" s="12"/>
-      <c r="H52" s="12"/>
-      <c r="I52" s="13" t="str">
+    <row r="52" ht="30" spans="1:14">
+      <c r="A52" s="11">
+        <v>46289</v>
+      </c>
+      <c r="B52" s="12">
+        <v>360</v>
+      </c>
+      <c r="C52" s="12">
+        <v>30</v>
+      </c>
+      <c r="D52" s="12">
+        <v>240</v>
+      </c>
+      <c r="E52" s="12">
+        <v>30</v>
+      </c>
+      <c r="F52" s="12">
+        <v>150</v>
+      </c>
+      <c r="G52" s="12">
+        <v>3</v>
+      </c>
+      <c r="H52" s="12">
+        <v>30</v>
+      </c>
+      <c r="I52" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="13" t="str">
+        <v>840</v>
+      </c>
+      <c r="J52" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="14"/>
-      <c r="L52" s="14"/>
-      <c r="M52" s="14"/>
-      <c r="N52" s="15"/>
+        <v>600</v>
+      </c>
+      <c r="K52" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L52" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M52" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="N52" s="15" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="53" spans="1:14">
       <c r="A53" s="11"/>
@@ -11581,28 +11608,33 @@
     <mergeCell ref="A4:N4"/>
   </mergeCells>
   <conditionalFormatting sqref="J51">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J52">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J29:J44">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J6:J28 J45:J50 J52:J401">
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="lessThan">
+  <conditionalFormatting sqref="J6:J28 J45:J50 J53:J401">
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K51 K6:K50 K52:K401">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K52 K6:K51 K53:K401">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L51 L6:L50 L52:L401">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L52 L6:L51 L53:L401">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M51 M6:M50 M52:M401">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M52 M6:M51 M53:M401">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
   </dataValidations>

--- a/12623065.xlsx
+++ b/12623065.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20370" windowHeight="8520" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="104">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -337,6 +337,9 @@
   </si>
   <si>
     <t>Feeling tired because of headache.</t>
+  </si>
+  <si>
+    <t>Attend all calsses today.</t>
   </si>
 </sst>
 </file>
@@ -3921,26 +3924,48 @@
       </c>
     </row>
     <row r="53" spans="1:14">
-      <c r="A53" s="11"/>
-      <c r="B53" s="12"/>
-      <c r="C53" s="12"/>
-      <c r="D53" s="12"/>
-      <c r="E53" s="12"/>
-      <c r="F53" s="12"/>
-      <c r="G53" s="12"/>
-      <c r="H53" s="12"/>
-      <c r="I53" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="14"/>
-      <c r="L53" s="14"/>
-      <c r="M53" s="14"/>
-      <c r="N53" s="15"/>
+      <c r="A53" s="11">
+        <v>46290</v>
+      </c>
+      <c r="B53" s="12">
+        <v>420</v>
+      </c>
+      <c r="C53" s="12">
+        <v>30</v>
+      </c>
+      <c r="D53" s="12">
+        <v>240</v>
+      </c>
+      <c r="E53" s="12">
+        <v>120</v>
+      </c>
+      <c r="F53" s="12">
+        <v>250</v>
+      </c>
+      <c r="G53" s="12">
+        <v>5</v>
+      </c>
+      <c r="H53" s="12">
+        <v>30</v>
+      </c>
+      <c r="I53" s="13">
+        <v>1090</v>
+      </c>
+      <c r="J53" s="13">
+        <v>350</v>
+      </c>
+      <c r="K53" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="L53" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M53" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N53" s="15" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="54" spans="1:14">
       <c r="A54" s="11"/>
@@ -11628,13 +11653,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K52 K6:K51 K53:K401">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K401">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L52 L6:L51 L53:L401">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L401">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M52 M6:M51 M53:M401">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M401">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
   </dataValidations>

--- a/12623065.xlsx
+++ b/12623065.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20370" windowHeight="8520" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="105">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -333,13 +333,16 @@
     <t>Busy day.</t>
   </si>
   <si>
-    <t xml:space="preserve">Today I had my CA , and it went good. Yesterday i studied almost since 2 am. </t>
+    <t>Today I had my CA , and it went good. Yesterday i studied almost since 2 am.</t>
   </si>
   <si>
     <t>Feeling tired because of headache.</t>
   </si>
   <si>
     <t>Attend all calsses today.</t>
+  </si>
+  <si>
+    <t>focusing more on studies.</t>
   </si>
 </sst>
 </file>
@@ -3968,26 +3971,50 @@
       </c>
     </row>
     <row r="54" spans="1:14">
-      <c r="A54" s="11"/>
-      <c r="B54" s="12"/>
-      <c r="C54" s="12"/>
-      <c r="D54" s="12"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="13" t="str">
+      <c r="A54" s="11">
+        <v>46291</v>
+      </c>
+      <c r="B54" s="12">
+        <v>300</v>
+      </c>
+      <c r="C54" s="12">
+        <v>30</v>
+      </c>
+      <c r="D54" s="12">
+        <v>300</v>
+      </c>
+      <c r="E54" s="12">
+        <v>180</v>
+      </c>
+      <c r="F54" s="12">
+        <v>150</v>
+      </c>
+      <c r="G54" s="12">
+        <v>3</v>
+      </c>
+      <c r="H54" s="12">
+        <v>30</v>
+      </c>
+      <c r="I54" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="13" t="str">
+        <v>990</v>
+      </c>
+      <c r="J54" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="14"/>
-      <c r="L54" s="14"/>
-      <c r="M54" s="14"/>
-      <c r="N54" s="15"/>
+        <v>450</v>
+      </c>
+      <c r="K54" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="L54" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="M54" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N54" s="15" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="55" spans="1:14">
       <c r="A55" s="11"/>

--- a/12623065.xlsx
+++ b/12623065.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20370" windowHeight="7500" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="107">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -343,6 +343,12 @@
   </si>
   <si>
     <t>focusing more on studies.</t>
+  </si>
+  <si>
+    <t>Stressed</t>
+  </si>
+  <si>
+    <t>Not feeling good.</t>
   </si>
 </sst>
 </file>
@@ -4017,26 +4023,50 @@
       </c>
     </row>
     <row r="55" spans="1:14">
-      <c r="A55" s="11"/>
-      <c r="B55" s="12"/>
-      <c r="C55" s="12"/>
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="12"/>
-      <c r="I55" s="13" t="str">
+      <c r="A55" s="11">
+        <v>46292</v>
+      </c>
+      <c r="B55" s="12">
+        <v>300</v>
+      </c>
+      <c r="C55" s="12">
+        <v>30</v>
+      </c>
+      <c r="D55" s="12">
+        <v>200</v>
+      </c>
+      <c r="E55" s="12">
+        <v>40</v>
+      </c>
+      <c r="F55" s="12">
+        <v>0</v>
+      </c>
+      <c r="G55" s="12">
+        <v>0</v>
+      </c>
+      <c r="H55" s="12">
+        <v>30</v>
+      </c>
+      <c r="I55" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="13" t="str">
+        <v>600</v>
+      </c>
+      <c r="J55" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="14"/>
-      <c r="L55" s="14"/>
-      <c r="M55" s="14"/>
-      <c r="N55" s="15"/>
+        <v>840</v>
+      </c>
+      <c r="K55" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="L55" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="M55" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="N55" s="15" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="56" spans="1:14">
       <c r="A56" s="11"/>

--- a/12623065.xlsx
+++ b/12623065.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20370" windowHeight="7500" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20370" windowHeight="6900" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="108">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -349,6 +349,9 @@
   </si>
   <si>
     <t>Not feeling good.</t>
+  </si>
+  <si>
+    <t>Feeling so happy coming back to home and little tired because of travelling</t>
   </si>
 </sst>
 </file>
@@ -4068,27 +4071,51 @@
         <v>106</v>
       </c>
     </row>
-    <row r="56" spans="1:14">
-      <c r="A56" s="11"/>
-      <c r="B56" s="12"/>
-      <c r="C56" s="12"/>
-      <c r="D56" s="12"/>
-      <c r="E56" s="12"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="12"/>
-      <c r="H56" s="12"/>
-      <c r="I56" s="13" t="str">
+    <row r="56" ht="45" spans="1:14">
+      <c r="A56" s="11">
+        <v>46293</v>
+      </c>
+      <c r="B56" s="12">
+        <v>300</v>
+      </c>
+      <c r="C56" s="12">
+        <v>30</v>
+      </c>
+      <c r="D56" s="12">
+        <v>60</v>
+      </c>
+      <c r="E56" s="12">
+        <v>20</v>
+      </c>
+      <c r="F56" s="12">
+        <v>0</v>
+      </c>
+      <c r="G56" s="12">
+        <v>0</v>
+      </c>
+      <c r="H56" s="12">
+        <v>30</v>
+      </c>
+      <c r="I56" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="13" t="str">
+        <v>440</v>
+      </c>
+      <c r="J56" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="14"/>
-      <c r="L56" s="14"/>
-      <c r="M56" s="14"/>
-      <c r="N56" s="15"/>
+        <v>1000</v>
+      </c>
+      <c r="K56" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L56" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M56" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N56" s="15" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="57" spans="1:14">
       <c r="A57" s="11"/>

--- a/12623065.xlsx
+++ b/12623065.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20370" windowHeight="6900" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20370" windowHeight="7500" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="109">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -352,6 +352,9 @@
   </si>
   <si>
     <t>Feeling so happy coming back to home and little tired because of travelling</t>
+  </si>
+  <si>
+    <t>Completed today's routine as planned.</t>
   </si>
 </sst>
 </file>
@@ -4117,27 +4120,51 @@
         <v>107</v>
       </c>
     </row>
-    <row r="57" spans="1:14">
-      <c r="A57" s="11"/>
-      <c r="B57" s="12"/>
-      <c r="C57" s="12"/>
-      <c r="D57" s="12"/>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="12"/>
-      <c r="I57" s="13" t="str">
+    <row r="57" ht="30" spans="1:14">
+      <c r="A57" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B57" s="12">
+        <v>360</v>
+      </c>
+      <c r="C57" s="12">
+        <v>30</v>
+      </c>
+      <c r="D57" s="12">
+        <v>120</v>
+      </c>
+      <c r="E57" s="12">
+        <v>40</v>
+      </c>
+      <c r="F57" s="12">
+        <v>0</v>
+      </c>
+      <c r="G57" s="12">
+        <v>0</v>
+      </c>
+      <c r="H57" s="12">
+        <v>20</v>
+      </c>
+      <c r="I57" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="13" t="str">
+        <v>570</v>
+      </c>
+      <c r="J57" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="14"/>
-      <c r="L57" s="14"/>
-      <c r="M57" s="14"/>
-      <c r="N57" s="15"/>
+        <v>870</v>
+      </c>
+      <c r="K57" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="L57" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="M57" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N57" s="15" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="58" spans="1:14">
       <c r="A58" s="11"/>

--- a/12623065.xlsx
+++ b/12623065.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20370" windowHeight="7500" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20370" windowHeight="6900" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="110">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -355,6 +355,9 @@
   </si>
   <si>
     <t>Completed today's routine as planned.</t>
+  </si>
+  <si>
+    <t>Had such a great time today.</t>
   </si>
 </sst>
 </file>
@@ -4167,26 +4170,50 @@
       </c>
     </row>
     <row r="58" spans="1:14">
-      <c r="A58" s="11"/>
-      <c r="B58" s="12"/>
-      <c r="C58" s="12"/>
-      <c r="D58" s="12"/>
-      <c r="E58" s="12"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="12"/>
-      <c r="H58" s="12"/>
-      <c r="I58" s="13" t="str">
+      <c r="A58" s="11">
+        <v>46295</v>
+      </c>
+      <c r="B58" s="12">
+        <v>420</v>
+      </c>
+      <c r="C58" s="12">
+        <v>30</v>
+      </c>
+      <c r="D58" s="12">
+        <v>180</v>
+      </c>
+      <c r="E58" s="12">
+        <v>60</v>
+      </c>
+      <c r="F58" s="12">
+        <v>0</v>
+      </c>
+      <c r="G58" s="12">
+        <v>0</v>
+      </c>
+      <c r="H58" s="12">
+        <v>30</v>
+      </c>
+      <c r="I58" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="13" t="str">
+        <v>720</v>
+      </c>
+      <c r="J58" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="14"/>
-      <c r="L58" s="14"/>
-      <c r="M58" s="14"/>
-      <c r="N58" s="15"/>
+        <v>720</v>
+      </c>
+      <c r="K58" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L58" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M58" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N58" s="15" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="59" spans="1:14">
       <c r="A59" s="11"/>

--- a/12623065.xlsx
+++ b/12623065.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20370" windowHeight="6900" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20370" windowHeight="7500" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="110">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4215,27 +4215,51 @@
         <v>109</v>
       </c>
     </row>
-    <row r="59" spans="1:14">
-      <c r="A59" s="11"/>
-      <c r="B59" s="12"/>
-      <c r="C59" s="12"/>
-      <c r="D59" s="12"/>
-      <c r="E59" s="12"/>
-      <c r="F59" s="12"/>
-      <c r="G59" s="12"/>
-      <c r="H59" s="12"/>
-      <c r="I59" s="13" t="str">
+    <row r="59" ht="30" spans="1:14">
+      <c r="A59" s="11">
+        <v>46296</v>
+      </c>
+      <c r="B59" s="12">
+        <v>360</v>
+      </c>
+      <c r="C59" s="12">
+        <v>30</v>
+      </c>
+      <c r="D59" s="12">
+        <v>300</v>
+      </c>
+      <c r="E59" s="12">
+        <v>120</v>
+      </c>
+      <c r="F59" s="12">
+        <v>0</v>
+      </c>
+      <c r="G59" s="12">
+        <v>0</v>
+      </c>
+      <c r="H59" s="12">
+        <v>40</v>
+      </c>
+      <c r="I59" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="13" t="str">
+        <v>850</v>
+      </c>
+      <c r="J59" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="14"/>
-      <c r="L59" s="14"/>
-      <c r="M59" s="14"/>
-      <c r="N59" s="15"/>
+        <v>590</v>
+      </c>
+      <c r="K59" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L59" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M59" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N59" s="15" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="60" spans="1:14">
       <c r="A60" s="11"/>

--- a/12623065.xlsx
+++ b/12623065.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20370" windowHeight="7500" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="111">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -358,6 +358,9 @@
   </si>
   <si>
     <t>Had such a great time today.</t>
+  </si>
+  <si>
+    <t>Focused on studies and daily tasks.</t>
   </si>
 </sst>
 </file>
@@ -4261,27 +4264,51 @@
         <v>108</v>
       </c>
     </row>
-    <row r="60" spans="1:14">
-      <c r="A60" s="11"/>
-      <c r="B60" s="12"/>
-      <c r="C60" s="12"/>
-      <c r="D60" s="12"/>
-      <c r="E60" s="12"/>
-      <c r="F60" s="12"/>
-      <c r="G60" s="12"/>
-      <c r="H60" s="12"/>
-      <c r="I60" s="13" t="str">
+    <row r="60" ht="30" spans="1:14">
+      <c r="A60" s="11">
+        <v>46297</v>
+      </c>
+      <c r="B60" s="12">
+        <v>360</v>
+      </c>
+      <c r="C60" s="12">
+        <v>30</v>
+      </c>
+      <c r="D60" s="12">
+        <v>360</v>
+      </c>
+      <c r="E60" s="12">
+        <v>120</v>
+      </c>
+      <c r="F60" s="12">
+        <v>0</v>
+      </c>
+      <c r="G60" s="12">
+        <v>0</v>
+      </c>
+      <c r="H60" s="12">
+        <v>40</v>
+      </c>
+      <c r="I60" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="13" t="str">
+        <v>910</v>
+      </c>
+      <c r="J60" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="14"/>
-      <c r="L60" s="14"/>
-      <c r="M60" s="14"/>
-      <c r="N60" s="15"/>
+        <v>530</v>
+      </c>
+      <c r="K60" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L60" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M60" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N60" s="15" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="61" spans="1:14">
       <c r="A61" s="11"/>

--- a/12623065.xlsx
+++ b/12623065.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="112">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -361,6 +361,9 @@
   </si>
   <si>
     <t>Focused on studies and daily tasks.</t>
+  </si>
+  <si>
+    <t>Completed the routine with some adjustments.</t>
   </si>
 </sst>
 </file>
@@ -4310,27 +4313,51 @@
         <v>110</v>
       </c>
     </row>
-    <row r="61" spans="1:14">
-      <c r="A61" s="11"/>
-      <c r="B61" s="12"/>
-      <c r="C61" s="12"/>
-      <c r="D61" s="12"/>
-      <c r="E61" s="12"/>
-      <c r="F61" s="12"/>
-      <c r="G61" s="12"/>
-      <c r="H61" s="12"/>
-      <c r="I61" s="13" t="str">
+    <row r="61" ht="30" spans="1:14">
+      <c r="A61" s="11">
+        <v>46298</v>
+      </c>
+      <c r="B61" s="12">
+        <v>420</v>
+      </c>
+      <c r="C61" s="12">
+        <v>30</v>
+      </c>
+      <c r="D61" s="12">
+        <v>300</v>
+      </c>
+      <c r="E61" s="12">
+        <v>60</v>
+      </c>
+      <c r="F61" s="12">
+        <v>0</v>
+      </c>
+      <c r="G61" s="12">
+        <v>0</v>
+      </c>
+      <c r="H61" s="12">
+        <v>40</v>
+      </c>
+      <c r="I61" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="13" t="str">
+        <v>850</v>
+      </c>
+      <c r="J61" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K61" s="14"/>
-      <c r="L61" s="14"/>
-      <c r="M61" s="14"/>
-      <c r="N61" s="15"/>
+        <v>590</v>
+      </c>
+      <c r="K61" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L61" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M61" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N61" s="15" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="62" spans="1:14">
       <c r="A62" s="11"/>

--- a/12623065.xlsx
+++ b/12623065.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="113">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -364,6 +364,9 @@
   </si>
   <si>
     <t>Completed the routine with some adjustments.</t>
+  </si>
+  <si>
+    <t>Routine was affected by other activities today.</t>
   </si>
 </sst>
 </file>
@@ -4359,27 +4362,51 @@
         <v>111</v>
       </c>
     </row>
-    <row r="62" spans="1:14">
-      <c r="A62" s="11"/>
-      <c r="B62" s="12"/>
-      <c r="C62" s="12"/>
-      <c r="D62" s="12"/>
-      <c r="E62" s="12"/>
-      <c r="F62" s="12"/>
-      <c r="G62" s="12"/>
-      <c r="H62" s="12"/>
-      <c r="I62" s="13" t="str">
+    <row r="62" ht="30" spans="1:14">
+      <c r="A62" s="11">
+        <v>46299</v>
+      </c>
+      <c r="B62" s="12">
+        <v>420</v>
+      </c>
+      <c r="C62" s="12">
+        <v>30</v>
+      </c>
+      <c r="D62" s="12">
+        <v>120</v>
+      </c>
+      <c r="E62" s="12">
+        <v>50</v>
+      </c>
+      <c r="F62" s="12">
+        <v>0</v>
+      </c>
+      <c r="G62" s="12">
+        <v>0</v>
+      </c>
+      <c r="H62" s="12">
+        <v>30</v>
+      </c>
+      <c r="I62" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J62" s="13" t="str">
+        <v>650</v>
+      </c>
+      <c r="J62" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K62" s="14"/>
-      <c r="L62" s="14"/>
-      <c r="M62" s="14"/>
-      <c r="N62" s="15"/>
+        <v>790</v>
+      </c>
+      <c r="K62" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="L62" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="M62" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N62" s="15" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="63" spans="1:14">
       <c r="A63" s="11"/>

--- a/12623065.xlsx
+++ b/12623065.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="114">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -367,6 +367,9 @@
   </si>
   <si>
     <t>Routine was affected by other activities today.</t>
+  </si>
+  <si>
+    <t>Had a productive and well -managed day.</t>
   </si>
 </sst>
 </file>
@@ -4408,27 +4411,51 @@
         <v>112</v>
       </c>
     </row>
-    <row r="63" spans="1:14">
-      <c r="A63" s="11"/>
-      <c r="B63" s="12"/>
-      <c r="C63" s="12"/>
-      <c r="D63" s="12"/>
-      <c r="E63" s="12"/>
-      <c r="F63" s="12"/>
-      <c r="G63" s="12"/>
-      <c r="H63" s="12"/>
-      <c r="I63" s="13" t="str">
+    <row r="63" ht="30" spans="1:14">
+      <c r="A63" s="11">
+        <v>46300</v>
+      </c>
+      <c r="B63" s="12">
+        <v>360</v>
+      </c>
+      <c r="C63" s="12">
+        <v>30</v>
+      </c>
+      <c r="D63" s="12">
+        <v>300</v>
+      </c>
+      <c r="E63" s="12">
+        <v>120</v>
+      </c>
+      <c r="F63" s="12">
+        <v>300</v>
+      </c>
+      <c r="G63" s="12">
+        <v>6</v>
+      </c>
+      <c r="H63" s="12">
+        <v>30</v>
+      </c>
+      <c r="I63" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="13" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J63" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K63" s="14"/>
-      <c r="L63" s="14"/>
-      <c r="M63" s="14"/>
-      <c r="N63" s="15"/>
+        <v>300</v>
+      </c>
+      <c r="K63" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="L63" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="M63" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N63" s="15" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="64" spans="1:14">
       <c r="A64" s="11"/>

--- a/12623065.xlsx
+++ b/12623065.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="115">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -370,6 +370,9 @@
   </si>
   <si>
     <t>Had a productive and well -managed day.</t>
+  </si>
+  <si>
+    <t>Attend the classes.</t>
   </si>
 </sst>
 </file>
@@ -4458,26 +4461,50 @@
       </c>
     </row>
     <row r="64" spans="1:14">
-      <c r="A64" s="11"/>
-      <c r="B64" s="12"/>
-      <c r="C64" s="12"/>
-      <c r="D64" s="12"/>
-      <c r="E64" s="12"/>
-      <c r="F64" s="12"/>
-      <c r="G64" s="12"/>
-      <c r="H64" s="12"/>
-      <c r="I64" s="13" t="str">
+      <c r="A64" s="11">
+        <v>46301</v>
+      </c>
+      <c r="B64" s="12">
+        <v>360</v>
+      </c>
+      <c r="C64" s="12">
+        <v>30</v>
+      </c>
+      <c r="D64" s="12">
+        <v>360</v>
+      </c>
+      <c r="E64" s="12">
+        <v>180</v>
+      </c>
+      <c r="F64" s="12">
+        <v>300</v>
+      </c>
+      <c r="G64" s="12">
+        <v>6</v>
+      </c>
+      <c r="H64" s="12">
+        <v>20</v>
+      </c>
+      <c r="I64" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J64" s="13" t="str">
+        <v>1250</v>
+      </c>
+      <c r="J64" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K64" s="14"/>
-      <c r="L64" s="14"/>
-      <c r="M64" s="14"/>
-      <c r="N64" s="15"/>
+        <v>190</v>
+      </c>
+      <c r="K64" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="L64" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="M64" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N64" s="15" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="65" spans="1:14">
       <c r="A65" s="11"/>

--- a/12623065.xlsx
+++ b/12623065.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="116">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -373,6 +373,9 @@
   </si>
   <si>
     <t>Attend the classes.</t>
+  </si>
+  <si>
+    <t>Stayed focused on the planned activities.</t>
   </si>
 </sst>
 </file>
@@ -4506,27 +4509,51 @@
         <v>114</v>
       </c>
     </row>
-    <row r="65" spans="1:14">
-      <c r="A65" s="11"/>
-      <c r="B65" s="12"/>
-      <c r="C65" s="12"/>
-      <c r="D65" s="12"/>
-      <c r="E65" s="12"/>
-      <c r="F65" s="12"/>
-      <c r="G65" s="12"/>
-      <c r="H65" s="12"/>
-      <c r="I65" s="13" t="str">
+    <row r="65" ht="30" spans="1:14">
+      <c r="A65" s="11">
+        <v>46302</v>
+      </c>
+      <c r="B65" s="12">
+        <v>360</v>
+      </c>
+      <c r="C65" s="12">
+        <v>30</v>
+      </c>
+      <c r="D65" s="12">
+        <v>300</v>
+      </c>
+      <c r="E65" s="12">
+        <v>180</v>
+      </c>
+      <c r="F65" s="12">
+        <v>350</v>
+      </c>
+      <c r="G65" s="12">
+        <v>7</v>
+      </c>
+      <c r="H65" s="12">
+        <v>20</v>
+      </c>
+      <c r="I65" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J65" s="13" t="str">
+        <v>1240</v>
+      </c>
+      <c r="J65" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K65" s="14"/>
-      <c r="L65" s="14"/>
-      <c r="M65" s="14"/>
-      <c r="N65" s="15"/>
+        <v>200</v>
+      </c>
+      <c r="K65" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="L65" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="M65" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N65" s="15" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="66" spans="1:14">
       <c r="A66" s="11"/>

--- a/12623065.xlsx
+++ b/12623065.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="117">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -376,6 +376,9 @@
   </si>
   <si>
     <t>Stayed focused on the planned activities.</t>
+  </si>
+  <si>
+    <t>Had a productive day.</t>
   </si>
 </sst>
 </file>
@@ -4556,26 +4559,50 @@
       </c>
     </row>
     <row r="66" spans="1:14">
-      <c r="A66" s="11"/>
-      <c r="B66" s="12"/>
-      <c r="C66" s="12"/>
-      <c r="D66" s="12"/>
-      <c r="E66" s="12"/>
-      <c r="F66" s="12"/>
-      <c r="G66" s="12"/>
-      <c r="H66" s="12"/>
-      <c r="I66" s="13" t="str">
+      <c r="A66" s="11">
+        <v>46303</v>
+      </c>
+      <c r="B66" s="12">
+        <v>360</v>
+      </c>
+      <c r="C66" s="12">
+        <v>30</v>
+      </c>
+      <c r="D66" s="12">
+        <v>240</v>
+      </c>
+      <c r="E66" s="12">
+        <v>120</v>
+      </c>
+      <c r="F66" s="12">
+        <v>200</v>
+      </c>
+      <c r="G66" s="12">
+        <v>4</v>
+      </c>
+      <c r="H66" s="12">
+        <v>30</v>
+      </c>
+      <c r="I66" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J66" s="13" t="str">
+        <v>980</v>
+      </c>
+      <c r="J66" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K66" s="14"/>
-      <c r="L66" s="14"/>
-      <c r="M66" s="14"/>
-      <c r="N66" s="15"/>
+        <v>460</v>
+      </c>
+      <c r="K66" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="L66" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="M66" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N66" s="15" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="67" spans="1:14">
       <c r="A67" s="11"/>

--- a/12623065.xlsx
+++ b/12623065.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="118">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -379,6 +379,9 @@
   </si>
   <si>
     <t>Had a productive day.</t>
+  </si>
+  <si>
+    <t>Good day.</t>
   </si>
 </sst>
 </file>
@@ -4605,26 +4608,50 @@
       </c>
     </row>
     <row r="67" spans="1:14">
-      <c r="A67" s="11"/>
-      <c r="B67" s="12"/>
-      <c r="C67" s="12"/>
-      <c r="D67" s="12"/>
-      <c r="E67" s="12"/>
-      <c r="F67" s="12"/>
-      <c r="G67" s="12"/>
-      <c r="H67" s="12"/>
-      <c r="I67" s="13" t="str">
+      <c r="A67" s="11">
+        <v>46304</v>
+      </c>
+      <c r="B67" s="12">
+        <v>360</v>
+      </c>
+      <c r="C67" s="12">
+        <v>30</v>
+      </c>
+      <c r="D67" s="12">
+        <v>300</v>
+      </c>
+      <c r="E67" s="12">
+        <v>120</v>
+      </c>
+      <c r="F67" s="12">
+        <v>0</v>
+      </c>
+      <c r="G67" s="12">
+        <v>0</v>
+      </c>
+      <c r="H67" s="12">
+        <v>40</v>
+      </c>
+      <c r="I67" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J67" s="13" t="str">
+        <v>850</v>
+      </c>
+      <c r="J67" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K67" s="14"/>
-      <c r="L67" s="14"/>
-      <c r="M67" s="14"/>
-      <c r="N67" s="15"/>
+        <v>590</v>
+      </c>
+      <c r="K67" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="L67" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="M67" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N67" s="15" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="68" spans="1:14">
       <c r="A68" s="11"/>

--- a/12623065.xlsx
+++ b/12623065.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="118">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4654,48 +4654,96 @@
       </c>
     </row>
     <row r="68" spans="1:14">
-      <c r="A68" s="11"/>
-      <c r="B68" s="12"/>
-      <c r="C68" s="12"/>
-      <c r="D68" s="12"/>
-      <c r="E68" s="12"/>
-      <c r="F68" s="12"/>
-      <c r="G68" s="12"/>
-      <c r="H68" s="12"/>
-      <c r="I68" s="13" t="str">
+      <c r="A68" s="11">
+        <v>46305</v>
+      </c>
+      <c r="B68" s="12">
+        <v>360</v>
+      </c>
+      <c r="C68" s="12">
+        <v>30</v>
+      </c>
+      <c r="D68" s="12">
+        <v>240</v>
+      </c>
+      <c r="E68" s="12">
+        <v>60</v>
+      </c>
+      <c r="F68" s="12">
+        <v>0</v>
+      </c>
+      <c r="G68" s="12">
+        <v>0</v>
+      </c>
+      <c r="H68" s="12">
+        <v>30</v>
+      </c>
+      <c r="I68" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J68" s="13" t="str">
+        <v>720</v>
+      </c>
+      <c r="J68" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K68" s="14"/>
-      <c r="L68" s="14"/>
-      <c r="M68" s="14"/>
-      <c r="N68" s="15"/>
+        <v>720</v>
+      </c>
+      <c r="K68" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="L68" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="M68" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N68" s="15" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="69" spans="1:14">
-      <c r="A69" s="11"/>
-      <c r="B69" s="12"/>
-      <c r="C69" s="12"/>
-      <c r="D69" s="12"/>
-      <c r="E69" s="12"/>
-      <c r="F69" s="12"/>
-      <c r="G69" s="12"/>
-      <c r="H69" s="12"/>
-      <c r="I69" s="13" t="str">
+      <c r="A69" s="11">
+        <v>46306</v>
+      </c>
+      <c r="B69" s="12">
+        <v>240</v>
+      </c>
+      <c r="C69" s="12">
+        <v>40</v>
+      </c>
+      <c r="D69" s="12">
+        <v>300</v>
+      </c>
+      <c r="E69" s="12">
+        <v>60</v>
+      </c>
+      <c r="F69" s="12">
+        <v>0</v>
+      </c>
+      <c r="G69" s="12">
+        <v>0</v>
+      </c>
+      <c r="H69" s="12">
+        <v>30</v>
+      </c>
+      <c r="I69" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J69" s="13" t="str">
+        <v>670</v>
+      </c>
+      <c r="J69" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K69" s="14"/>
-      <c r="L69" s="14"/>
-      <c r="M69" s="14"/>
-      <c r="N69" s="15"/>
+        <v>770</v>
+      </c>
+      <c r="K69" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="L69" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="M69" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N69" s="15" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="70" spans="1:14">
       <c r="A70" s="11"/>

--- a/12623065.xlsx
+++ b/12623065.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="119">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -382,6 +382,9 @@
   </si>
   <si>
     <t>Good day.</t>
+  </si>
+  <si>
+    <t>I will work even harder towards my studies.</t>
   </si>
 </sst>
 </file>
@@ -4745,27 +4748,51 @@
         <v>96</v>
       </c>
     </row>
-    <row r="70" spans="1:14">
-      <c r="A70" s="11"/>
-      <c r="B70" s="12"/>
-      <c r="C70" s="12"/>
-      <c r="D70" s="12"/>
-      <c r="E70" s="12"/>
-      <c r="F70" s="12"/>
-      <c r="G70" s="12"/>
-      <c r="H70" s="12"/>
-      <c r="I70" s="13" t="str">
+    <row r="70" ht="30" spans="1:14">
+      <c r="A70" s="11">
+        <v>46307</v>
+      </c>
+      <c r="B70" s="12">
+        <v>300</v>
+      </c>
+      <c r="C70" s="12">
+        <v>30</v>
+      </c>
+      <c r="D70" s="12">
+        <v>420</v>
+      </c>
+      <c r="E70" s="12">
+        <v>60</v>
+      </c>
+      <c r="F70" s="12">
+        <v>0</v>
+      </c>
+      <c r="G70" s="12">
+        <v>0</v>
+      </c>
+      <c r="H70" s="12">
+        <v>20</v>
+      </c>
+      <c r="I70" s="13">
         <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
-        <v/>
-      </c>
-      <c r="J70" s="13" t="str">
+        <v>830</v>
+      </c>
+      <c r="J70" s="13">
         <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
-        <v/>
-      </c>
-      <c r="K70" s="14"/>
-      <c r="L70" s="14"/>
-      <c r="M70" s="14"/>
-      <c r="N70" s="15"/>
+        <v>610</v>
+      </c>
+      <c r="K70" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="L70" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="M70" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N70" s="15" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="71" spans="1:14">
       <c r="A71" s="11"/>

--- a/12623065.xlsx
+++ b/12623065.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="120">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -385,6 +385,9 @@
   </si>
   <si>
     <t>I will work even harder towards my studies.</t>
+  </si>
+  <si>
+    <t>Exam went well.</t>
   </si>
 </sst>
 </file>
@@ -4795,26 +4798,49 @@
       </c>
     </row>
     <row r="71" spans="1:14">
-      <c r="A71" s="11"/>
-      <c r="B71" s="12"/>
-      <c r="C71" s="12"/>
-      <c r="D71" s="12"/>
-      <c r="E71" s="12"/>
-      <c r="F71" s="12"/>
-      <c r="G71" s="12"/>
-      <c r="H71" s="12"/>
-      <c r="I71" s="13" t="str">
+      <c r="A71" s="11">
+        <v>46308</v>
+      </c>
+      <c r="B71" s="12">
+        <v>300</v>
+      </c>
+      <c r="C71" s="12">
+        <v>20</v>
+      </c>
+      <c r="D71" s="12">
+        <v>360</v>
+      </c>
+      <c r="E71" s="12">
+        <v>60</v>
+      </c>
+      <c r="F71" s="12">
+        <v>0</v>
+      </c>
+      <c r="G71" s="12">
+        <v>0</v>
+      </c>
+      <c r="H71" s="12">
+        <v>20</v>
+      </c>
+      <c r="I71" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J71" s="13" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K71" s="14"/>
-      <c r="L71" s="14"/>
-      <c r="M71" s="14"/>
-      <c r="N71" s="15"/>
+        <v>760</v>
+      </c>
+      <c r="J71" s="13">
+        <v>680</v>
+      </c>
+      <c r="K71" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="L71" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="M71" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N71" s="15" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="72" spans="1:14">
       <c r="A72" s="11"/>

--- a/12623065.xlsx
+++ b/12623065.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="121">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -388,6 +388,9 @@
   </si>
   <si>
     <t>Exam went well.</t>
+  </si>
+  <si>
+    <t>A little better than yesterday.</t>
   </si>
 </sst>
 </file>
@@ -4843,26 +4846,50 @@
       </c>
     </row>
     <row r="72" spans="1:14">
-      <c r="A72" s="11"/>
-      <c r="B72" s="12"/>
-      <c r="C72" s="12"/>
-      <c r="D72" s="12"/>
-      <c r="E72" s="12"/>
-      <c r="F72" s="12"/>
-      <c r="G72" s="12"/>
-      <c r="H72" s="12"/>
-      <c r="I72" s="13" t="str">
+      <c r="A72" s="11">
+        <v>46309</v>
+      </c>
+      <c r="B72" s="12">
+        <v>300</v>
+      </c>
+      <c r="C72" s="12">
+        <v>20</v>
+      </c>
+      <c r="D72" s="12">
+        <v>240</v>
+      </c>
+      <c r="E72" s="12">
+        <v>60</v>
+      </c>
+      <c r="F72" s="12">
+        <v>0</v>
+      </c>
+      <c r="G72" s="12">
+        <v>0</v>
+      </c>
+      <c r="H72" s="12">
+        <v>30</v>
+      </c>
+      <c r="I72" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J72" s="13" t="str">
+        <v>650</v>
+      </c>
+      <c r="J72" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K72" s="14"/>
-      <c r="L72" s="14"/>
-      <c r="M72" s="14"/>
-      <c r="N72" s="15"/>
+        <v>790</v>
+      </c>
+      <c r="K72" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="L72" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="M72" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N72" s="15" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="73" spans="1:14">
       <c r="A73" s="11"/>

--- a/12623065.xlsx
+++ b/12623065.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="122">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -391,6 +391,9 @@
   </si>
   <si>
     <t>A little better than yesterday.</t>
+  </si>
+  <si>
+    <t>Completed my regular activities.</t>
   </si>
 </sst>
 </file>
@@ -4891,27 +4894,51 @@
         <v>120</v>
       </c>
     </row>
-    <row r="73" spans="1:14">
-      <c r="A73" s="11"/>
-      <c r="B73" s="12"/>
-      <c r="C73" s="12"/>
-      <c r="D73" s="12"/>
-      <c r="E73" s="12"/>
-      <c r="F73" s="12"/>
-      <c r="G73" s="12"/>
-      <c r="H73" s="12"/>
-      <c r="I73" s="13" t="str">
+    <row r="73" ht="30" spans="1:14">
+      <c r="A73" s="11">
+        <v>46310</v>
+      </c>
+      <c r="B73" s="12">
+        <v>300</v>
+      </c>
+      <c r="C73" s="12">
+        <v>20</v>
+      </c>
+      <c r="D73" s="12">
+        <v>420</v>
+      </c>
+      <c r="E73" s="12">
+        <v>60</v>
+      </c>
+      <c r="F73" s="12">
+        <v>0</v>
+      </c>
+      <c r="G73" s="12">
+        <v>0</v>
+      </c>
+      <c r="H73" s="12">
+        <v>30</v>
+      </c>
+      <c r="I73" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J73" s="13" t="str">
+        <v>830</v>
+      </c>
+      <c r="J73" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K73" s="14"/>
-      <c r="L73" s="14"/>
-      <c r="M73" s="14"/>
-      <c r="N73" s="15"/>
+        <v>610</v>
+      </c>
+      <c r="K73" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="L73" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="M73" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N73" s="15" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="74" spans="1:14">
       <c r="A74" s="11"/>

--- a/12623065.xlsx
+++ b/12623065.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="123">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -394,6 +394,9 @@
   </si>
   <si>
     <t>Completed my regular activities.</t>
+  </si>
+  <si>
+    <t>Everything went smoothly.</t>
   </si>
 </sst>
 </file>
@@ -4941,26 +4944,50 @@
       </c>
     </row>
     <row r="74" spans="1:14">
-      <c r="A74" s="11"/>
-      <c r="B74" s="12"/>
-      <c r="C74" s="12"/>
-      <c r="D74" s="12"/>
-      <c r="E74" s="12"/>
-      <c r="F74" s="12"/>
-      <c r="G74" s="12"/>
-      <c r="H74" s="12"/>
-      <c r="I74" s="13" t="str">
+      <c r="A74" s="11">
+        <v>46311</v>
+      </c>
+      <c r="B74" s="12">
+        <v>240</v>
+      </c>
+      <c r="C74" s="12">
+        <v>20</v>
+      </c>
+      <c r="D74" s="12">
+        <v>360</v>
+      </c>
+      <c r="E74" s="12">
+        <v>60</v>
+      </c>
+      <c r="F74" s="12">
+        <v>0</v>
+      </c>
+      <c r="G74" s="12">
+        <v>0</v>
+      </c>
+      <c r="H74" s="12">
+        <v>30</v>
+      </c>
+      <c r="I74" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J74" s="13" t="str">
+        <v>710</v>
+      </c>
+      <c r="J74" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K74" s="14"/>
-      <c r="L74" s="14"/>
-      <c r="M74" s="14"/>
-      <c r="N74" s="15"/>
+        <v>730</v>
+      </c>
+      <c r="K74" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="L74" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="M74" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N74" s="15" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="75" spans="1:14">
       <c r="A75" s="11"/>

--- a/12623065.xlsx
+++ b/12623065.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="124">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -397,6 +397,9 @@
   </si>
   <si>
     <t>Everything went smoothly.</t>
+  </si>
+  <si>
+    <t>Midterm went well.</t>
   </si>
 </sst>
 </file>
@@ -4990,26 +4993,50 @@
       </c>
     </row>
     <row r="75" spans="1:14">
-      <c r="A75" s="11"/>
-      <c r="B75" s="12"/>
-      <c r="C75" s="12"/>
-      <c r="D75" s="12"/>
-      <c r="E75" s="12"/>
-      <c r="F75" s="12"/>
-      <c r="G75" s="12"/>
-      <c r="H75" s="12"/>
-      <c r="I75" s="13" t="str">
+      <c r="A75" s="11">
+        <v>46312</v>
+      </c>
+      <c r="B75" s="12">
+        <v>300</v>
+      </c>
+      <c r="C75" s="12">
+        <v>30</v>
+      </c>
+      <c r="D75" s="12">
+        <v>420</v>
+      </c>
+      <c r="E75" s="12">
+        <v>60</v>
+      </c>
+      <c r="F75" s="12">
+        <v>0</v>
+      </c>
+      <c r="G75" s="12">
+        <v>0</v>
+      </c>
+      <c r="H75" s="12">
+        <v>30</v>
+      </c>
+      <c r="I75" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J75" s="13" t="str">
+        <v>840</v>
+      </c>
+      <c r="J75" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K75" s="14"/>
-      <c r="L75" s="14"/>
-      <c r="M75" s="14"/>
-      <c r="N75" s="15"/>
+        <v>600</v>
+      </c>
+      <c r="K75" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="L75" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="M75" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N75" s="15" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="76" spans="1:14">
       <c r="A76" s="11"/>

--- a/12623065.xlsx
+++ b/12623065.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="125">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -400,6 +400,9 @@
   </si>
   <si>
     <t>Midterm went well.</t>
+  </si>
+  <si>
+    <t>Tired.</t>
   </si>
 </sst>
 </file>
@@ -5039,26 +5042,50 @@
       </c>
     </row>
     <row r="76" spans="1:14">
-      <c r="A76" s="11"/>
-      <c r="B76" s="12"/>
-      <c r="C76" s="12"/>
-      <c r="D76" s="12"/>
-      <c r="E76" s="12"/>
-      <c r="F76" s="12"/>
-      <c r="G76" s="12"/>
-      <c r="H76" s="12"/>
-      <c r="I76" s="13" t="str">
+      <c r="A76" s="11">
+        <v>46313</v>
+      </c>
+      <c r="B76" s="12">
+        <v>420</v>
+      </c>
+      <c r="C76" s="12">
+        <v>20</v>
+      </c>
+      <c r="D76" s="12">
+        <v>180</v>
+      </c>
+      <c r="E76" s="12">
+        <v>60</v>
+      </c>
+      <c r="F76" s="12">
+        <v>0</v>
+      </c>
+      <c r="G76" s="12">
+        <v>0</v>
+      </c>
+      <c r="H76" s="12">
+        <v>30</v>
+      </c>
+      <c r="I76" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J76" s="13" t="str">
+        <v>710</v>
+      </c>
+      <c r="J76" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K76" s="14"/>
-      <c r="L76" s="14"/>
-      <c r="M76" s="14"/>
-      <c r="N76" s="15"/>
+        <v>730</v>
+      </c>
+      <c r="K76" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="L76" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="M76" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="N76" s="15" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="77" spans="1:14">
       <c r="A77" s="11"/>

--- a/12623065.xlsx
+++ b/12623065.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="125">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -5088,26 +5088,50 @@
       </c>
     </row>
     <row r="77" spans="1:14">
-      <c r="A77" s="11"/>
-      <c r="B77" s="12"/>
-      <c r="C77" s="12"/>
-      <c r="D77" s="12"/>
-      <c r="E77" s="12"/>
-      <c r="F77" s="12"/>
-      <c r="G77" s="12"/>
-      <c r="H77" s="12"/>
-      <c r="I77" s="13" t="str">
+      <c r="A77" s="11">
+        <v>46314</v>
+      </c>
+      <c r="B77" s="12">
+        <v>420</v>
+      </c>
+      <c r="C77" s="12">
+        <v>20</v>
+      </c>
+      <c r="D77" s="12">
+        <v>180</v>
+      </c>
+      <c r="E77" s="12">
+        <v>120</v>
+      </c>
+      <c r="F77" s="12">
+        <v>50</v>
+      </c>
+      <c r="G77" s="12">
+        <v>1</v>
+      </c>
+      <c r="H77" s="12">
+        <v>30</v>
+      </c>
+      <c r="I77" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J77" s="13" t="str">
+        <v>820</v>
+      </c>
+      <c r="J77" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K77" s="14"/>
-      <c r="L77" s="14"/>
-      <c r="M77" s="14"/>
-      <c r="N77" s="15"/>
+        <v>620</v>
+      </c>
+      <c r="K77" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="L77" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="M77" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N77" s="15" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="78" spans="1:14">
       <c r="A78" s="11"/>

--- a/12623065.xlsx
+++ b/12623065.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="126">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -403,6 +403,9 @@
   </si>
   <si>
     <t>Tired.</t>
+  </si>
+  <si>
+    <t>Focused on academic task today.</t>
   </si>
 </sst>
 </file>
@@ -5133,27 +5136,51 @@
         <v>76</v>
       </c>
     </row>
-    <row r="78" spans="1:14">
-      <c r="A78" s="11"/>
-      <c r="B78" s="12"/>
-      <c r="C78" s="12"/>
-      <c r="D78" s="12"/>
-      <c r="E78" s="12"/>
-      <c r="F78" s="12"/>
-      <c r="G78" s="12"/>
-      <c r="H78" s="12"/>
-      <c r="I78" s="13" t="str">
+    <row r="78" ht="30" spans="1:14">
+      <c r="A78" s="11">
+        <v>46315</v>
+      </c>
+      <c r="B78" s="12">
+        <v>420</v>
+      </c>
+      <c r="C78" s="12">
+        <v>30</v>
+      </c>
+      <c r="D78" s="12">
+        <v>180</v>
+      </c>
+      <c r="E78" s="12">
+        <v>120</v>
+      </c>
+      <c r="F78" s="12">
+        <v>0</v>
+      </c>
+      <c r="G78" s="12">
+        <v>0</v>
+      </c>
+      <c r="H78" s="12">
+        <v>30</v>
+      </c>
+      <c r="I78" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J78" s="13" t="str">
+        <v>780</v>
+      </c>
+      <c r="J78" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K78" s="14"/>
-      <c r="L78" s="14"/>
-      <c r="M78" s="14"/>
-      <c r="N78" s="15"/>
+        <v>660</v>
+      </c>
+      <c r="K78" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="L78" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="M78" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N78" s="15" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="79" spans="1:14">
       <c r="A79" s="11"/>

--- a/12623065.xlsx
+++ b/12623065.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="127">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -406,6 +406,9 @@
   </si>
   <si>
     <t>Focused on academic task today.</t>
+  </si>
+  <si>
+    <t>Completed my task.</t>
   </si>
 </sst>
 </file>
@@ -5183,26 +5186,50 @@
       </c>
     </row>
     <row r="79" spans="1:14">
-      <c r="A79" s="11"/>
-      <c r="B79" s="12"/>
-      <c r="C79" s="12"/>
-      <c r="D79" s="12"/>
-      <c r="E79" s="12"/>
-      <c r="F79" s="12"/>
-      <c r="G79" s="12"/>
-      <c r="H79" s="12"/>
-      <c r="I79" s="13" t="str">
+      <c r="A79" s="11">
+        <v>46315</v>
+      </c>
+      <c r="B79" s="12">
+        <v>360</v>
+      </c>
+      <c r="C79" s="12">
+        <v>30</v>
+      </c>
+      <c r="D79" s="12">
+        <v>300</v>
+      </c>
+      <c r="E79" s="12">
+        <v>180</v>
+      </c>
+      <c r="F79" s="12">
+        <v>300</v>
+      </c>
+      <c r="G79" s="12">
+        <v>6</v>
+      </c>
+      <c r="H79" s="12">
+        <v>30</v>
+      </c>
+      <c r="I79" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J79" s="13" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J79" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K79" s="14"/>
-      <c r="L79" s="14"/>
-      <c r="M79" s="14"/>
-      <c r="N79" s="15"/>
+        <v>240</v>
+      </c>
+      <c r="K79" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="L79" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="M79" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N79" s="15" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="80" spans="1:14">
       <c r="A80" s="11"/>

--- a/12623065.xlsx
+++ b/12623065.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="127">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -5187,7 +5187,7 @@
     </row>
     <row r="79" spans="1:14">
       <c r="A79" s="11">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="B79" s="12">
         <v>360</v>
@@ -5232,26 +5232,50 @@
       </c>
     </row>
     <row r="80" spans="1:14">
-      <c r="A80" s="11"/>
-      <c r="B80" s="12"/>
-      <c r="C80" s="12"/>
-      <c r="D80" s="12"/>
-      <c r="E80" s="12"/>
-      <c r="F80" s="12"/>
-      <c r="G80" s="12"/>
-      <c r="H80" s="12"/>
-      <c r="I80" s="13" t="str">
+      <c r="A80" s="11">
+        <v>46317</v>
+      </c>
+      <c r="B80" s="12">
+        <v>360</v>
+      </c>
+      <c r="C80" s="12">
+        <v>30</v>
+      </c>
+      <c r="D80" s="12">
+        <v>240</v>
+      </c>
+      <c r="E80" s="12">
+        <v>180</v>
+      </c>
+      <c r="F80" s="12">
+        <v>200</v>
+      </c>
+      <c r="G80" s="12">
+        <v>4</v>
+      </c>
+      <c r="H80" s="12">
+        <v>30</v>
+      </c>
+      <c r="I80" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J80" s="13" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J80" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K80" s="14"/>
-      <c r="L80" s="14"/>
-      <c r="M80" s="14"/>
-      <c r="N80" s="15"/>
+        <v>400</v>
+      </c>
+      <c r="K80" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="L80" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="M80" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N80" s="15" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="81" spans="1:14">
       <c r="A81" s="11"/>

--- a/12623065.xlsx
+++ b/12623065.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="128">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -409,6 +409,9 @@
   </si>
   <si>
     <t>Completed my task.</t>
+  </si>
+  <si>
+    <t>CA project work still pending.</t>
   </si>
 </sst>
 </file>
@@ -5278,26 +5281,50 @@
       </c>
     </row>
     <row r="81" spans="1:14">
-      <c r="A81" s="11"/>
-      <c r="B81" s="12"/>
-      <c r="C81" s="12"/>
-      <c r="D81" s="12"/>
-      <c r="E81" s="12"/>
-      <c r="F81" s="12"/>
-      <c r="G81" s="12"/>
-      <c r="H81" s="12"/>
-      <c r="I81" s="13" t="str">
+      <c r="A81" s="11">
+        <v>46318</v>
+      </c>
+      <c r="B81" s="12">
+        <v>360</v>
+      </c>
+      <c r="C81" s="12">
+        <v>30</v>
+      </c>
+      <c r="D81" s="12">
+        <v>300</v>
+      </c>
+      <c r="E81" s="12">
+        <v>180</v>
+      </c>
+      <c r="F81" s="12">
+        <v>150</v>
+      </c>
+      <c r="G81" s="12">
+        <v>3</v>
+      </c>
+      <c r="H81" s="12">
+        <v>30</v>
+      </c>
+      <c r="I81" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J81" s="13" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J81" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K81" s="14"/>
-      <c r="L81" s="14"/>
-      <c r="M81" s="14"/>
-      <c r="N81" s="15"/>
+        <v>390</v>
+      </c>
+      <c r="K81" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="L81" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="M81" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N81" s="15" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="82" spans="1:14">
       <c r="A82" s="11"/>

--- a/12623065.xlsx
+++ b/12623065.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="129">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -412,6 +412,9 @@
   </si>
   <si>
     <t>CA project work still pending.</t>
+  </si>
+  <si>
+    <t>Had a good day and attended my mentor meeting today.</t>
   </si>
 </sst>
 </file>
@@ -5326,27 +5329,51 @@
         <v>127</v>
       </c>
     </row>
-    <row r="82" spans="1:14">
-      <c r="A82" s="11"/>
-      <c r="B82" s="12"/>
-      <c r="C82" s="12"/>
-      <c r="D82" s="12"/>
-      <c r="E82" s="12"/>
-      <c r="F82" s="12"/>
-      <c r="G82" s="12"/>
-      <c r="H82" s="12"/>
-      <c r="I82" s="13" t="str">
+    <row r="82" ht="30" spans="1:14">
+      <c r="A82" s="11">
+        <v>46319</v>
+      </c>
+      <c r="B82" s="12">
+        <v>420</v>
+      </c>
+      <c r="C82" s="12">
+        <v>30</v>
+      </c>
+      <c r="D82" s="12">
+        <v>240</v>
+      </c>
+      <c r="E82" s="12">
+        <v>240</v>
+      </c>
+      <c r="F82" s="12">
+        <v>100</v>
+      </c>
+      <c r="G82" s="12">
+        <v>2</v>
+      </c>
+      <c r="H82" s="12">
+        <v>20</v>
+      </c>
+      <c r="I82" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J82" s="13" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J82" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K82" s="14"/>
-      <c r="L82" s="14"/>
-      <c r="M82" s="14"/>
-      <c r="N82" s="15"/>
+        <v>390</v>
+      </c>
+      <c r="K82" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="L82" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="M82" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N82" s="15" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="83" spans="1:14">
       <c r="A83" s="11"/>

--- a/12623065.xlsx
+++ b/12623065.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="130">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -415,6 +415,9 @@
   </si>
   <si>
     <t>Had a good day and attended my mentor meeting today.</t>
+  </si>
+  <si>
+    <t>All over good day.</t>
   </si>
 </sst>
 </file>
@@ -5376,26 +5379,50 @@
       </c>
     </row>
     <row r="83" spans="1:14">
-      <c r="A83" s="11"/>
-      <c r="B83" s="12"/>
-      <c r="C83" s="12"/>
-      <c r="D83" s="12"/>
-      <c r="E83" s="12"/>
-      <c r="F83" s="12"/>
-      <c r="G83" s="12"/>
-      <c r="H83" s="12"/>
-      <c r="I83" s="13" t="str">
+      <c r="A83" s="11">
+        <v>46320</v>
+      </c>
+      <c r="B83" s="12">
+        <v>300</v>
+      </c>
+      <c r="C83" s="12">
+        <v>30</v>
+      </c>
+      <c r="D83" s="12">
+        <v>300</v>
+      </c>
+      <c r="E83" s="12">
+        <v>180</v>
+      </c>
+      <c r="F83" s="12">
+        <v>0</v>
+      </c>
+      <c r="G83" s="12">
+        <v>0</v>
+      </c>
+      <c r="H83" s="12">
+        <v>30</v>
+      </c>
+      <c r="I83" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J83" s="13" t="str">
+        <v>840</v>
+      </c>
+      <c r="J83" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K83" s="14"/>
-      <c r="L83" s="14"/>
-      <c r="M83" s="14"/>
-      <c r="N83" s="15"/>
+        <v>600</v>
+      </c>
+      <c r="K83" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="L83" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="M83" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N83" s="15" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="84" spans="1:14">
       <c r="A84" s="11"/>

--- a/12623065.xlsx
+++ b/12623065.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="131">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -418,6 +418,9 @@
   </si>
   <si>
     <t>All over good day.</t>
+  </si>
+  <si>
+    <t>It was a hectic day today.</t>
   </si>
 </sst>
 </file>
@@ -5425,26 +5428,50 @@
       </c>
     </row>
     <row r="84" spans="1:14">
-      <c r="A84" s="11"/>
-      <c r="B84" s="12"/>
-      <c r="C84" s="12"/>
-      <c r="D84" s="12"/>
-      <c r="E84" s="12"/>
-      <c r="F84" s="12"/>
-      <c r="G84" s="12"/>
-      <c r="H84" s="12"/>
-      <c r="I84" s="13" t="str">
+      <c r="A84" s="11">
+        <v>46321</v>
+      </c>
+      <c r="B84" s="12">
+        <v>360</v>
+      </c>
+      <c r="C84" s="12">
+        <v>30</v>
+      </c>
+      <c r="D84" s="12">
+        <v>300</v>
+      </c>
+      <c r="E84" s="12">
+        <v>240</v>
+      </c>
+      <c r="F84" s="12">
+        <v>0</v>
+      </c>
+      <c r="G84" s="12">
+        <v>0</v>
+      </c>
+      <c r="H84" s="12">
+        <v>30</v>
+      </c>
+      <c r="I84" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J84" s="13" t="str">
+        <v>960</v>
+      </c>
+      <c r="J84" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K84" s="14"/>
-      <c r="L84" s="14"/>
-      <c r="M84" s="14"/>
-      <c r="N84" s="15"/>
+        <v>480</v>
+      </c>
+      <c r="K84" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="L84" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="M84" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N84" s="15" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="85" spans="1:14">
       <c r="A85" s="11"/>

--- a/12623065.xlsx
+++ b/12623065.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="132">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -421,6 +421,9 @@
   </si>
   <si>
     <t>It was a hectic day today.</t>
+  </si>
+  <si>
+    <t>A day well invested.</t>
   </si>
 </sst>
 </file>
@@ -5474,26 +5477,50 @@
       </c>
     </row>
     <row r="85" spans="1:14">
-      <c r="A85" s="11"/>
-      <c r="B85" s="12"/>
-      <c r="C85" s="12"/>
-      <c r="D85" s="12"/>
-      <c r="E85" s="12"/>
-      <c r="F85" s="12"/>
-      <c r="G85" s="12"/>
-      <c r="H85" s="12"/>
-      <c r="I85" s="13" t="str">
+      <c r="A85" s="11">
+        <v>46322</v>
+      </c>
+      <c r="B85" s="12">
+        <v>300</v>
+      </c>
+      <c r="C85" s="12">
+        <v>30</v>
+      </c>
+      <c r="D85" s="12">
+        <v>360</v>
+      </c>
+      <c r="E85" s="12">
+        <v>180</v>
+      </c>
+      <c r="F85" s="12">
+        <v>300</v>
+      </c>
+      <c r="G85" s="12">
+        <v>6</v>
+      </c>
+      <c r="H85" s="12">
+        <v>30</v>
+      </c>
+      <c r="I85" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J85" s="13" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J85" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K85" s="14"/>
-      <c r="L85" s="14"/>
-      <c r="M85" s="14"/>
-      <c r="N85" s="15"/>
+        <v>240</v>
+      </c>
+      <c r="K85" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="L85" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="M85" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N85" s="15" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="86" spans="1:14">
       <c r="A86" s="11"/>

--- a/12623065.xlsx
+++ b/12623065.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="132">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -5523,26 +5523,50 @@
       </c>
     </row>
     <row r="86" spans="1:14">
-      <c r="A86" s="11"/>
-      <c r="B86" s="12"/>
-      <c r="C86" s="12"/>
-      <c r="D86" s="12"/>
-      <c r="E86" s="12"/>
-      <c r="F86" s="12"/>
-      <c r="G86" s="12"/>
-      <c r="H86" s="12"/>
-      <c r="I86" s="13" t="str">
+      <c r="A86" s="11">
+        <v>46323</v>
+      </c>
+      <c r="B86" s="12">
+        <v>300</v>
+      </c>
+      <c r="C86" s="12">
+        <v>30</v>
+      </c>
+      <c r="D86" s="12">
+        <v>420</v>
+      </c>
+      <c r="E86" s="12">
+        <v>120</v>
+      </c>
+      <c r="F86" s="12">
+        <v>300</v>
+      </c>
+      <c r="G86" s="12">
+        <v>6</v>
+      </c>
+      <c r="H86" s="12">
+        <v>30</v>
+      </c>
+      <c r="I86" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J86" s="13" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J86" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K86" s="14"/>
-      <c r="L86" s="14"/>
-      <c r="M86" s="14"/>
-      <c r="N86" s="15"/>
+        <v>240</v>
+      </c>
+      <c r="K86" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="L86" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="M86" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N86" s="15" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="87" spans="1:14">
       <c r="A87" s="11"/>

--- a/12623065.xlsx
+++ b/12623065.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="133">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -424,6 +424,9 @@
   </si>
   <si>
     <t>A day well invested.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Today I had my CA , and it went good. </t>
   </si>
 </sst>
 </file>
@@ -5568,27 +5571,51 @@
         <v>96</v>
       </c>
     </row>
-    <row r="87" spans="1:14">
-      <c r="A87" s="11"/>
-      <c r="B87" s="12"/>
-      <c r="C87" s="12"/>
-      <c r="D87" s="12"/>
-      <c r="E87" s="12"/>
-      <c r="F87" s="12"/>
-      <c r="G87" s="12"/>
-      <c r="H87" s="12"/>
-      <c r="I87" s="13" t="str">
+    <row r="87" ht="30" spans="1:14">
+      <c r="A87" s="11">
+        <v>46324</v>
+      </c>
+      <c r="B87" s="12">
+        <v>300</v>
+      </c>
+      <c r="C87" s="12">
+        <v>30</v>
+      </c>
+      <c r="D87" s="12">
+        <v>300</v>
+      </c>
+      <c r="E87" s="12">
+        <v>120</v>
+      </c>
+      <c r="F87" s="12">
+        <v>200</v>
+      </c>
+      <c r="G87" s="12">
+        <v>4</v>
+      </c>
+      <c r="H87" s="12">
+        <v>30</v>
+      </c>
+      <c r="I87" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J87" s="13" t="str">
+        <v>980</v>
+      </c>
+      <c r="J87" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K87" s="14"/>
-      <c r="L87" s="14"/>
-      <c r="M87" s="14"/>
-      <c r="N87" s="15"/>
+        <v>460</v>
+      </c>
+      <c r="K87" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="L87" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="M87" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N87" s="15" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="88" spans="1:14">
       <c r="A88" s="11"/>

--- a/12623065.xlsx
+++ b/12623065.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="133">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -5618,26 +5618,50 @@
       </c>
     </row>
     <row r="88" spans="1:14">
-      <c r="A88" s="11"/>
-      <c r="B88" s="12"/>
-      <c r="C88" s="12"/>
-      <c r="D88" s="12"/>
-      <c r="E88" s="12"/>
-      <c r="F88" s="12"/>
-      <c r="G88" s="12"/>
-      <c r="H88" s="12"/>
-      <c r="I88" s="13" t="str">
+      <c r="A88" s="11">
+        <v>46325</v>
+      </c>
+      <c r="B88" s="12">
+        <v>300</v>
+      </c>
+      <c r="C88" s="12">
+        <v>30</v>
+      </c>
+      <c r="D88" s="12">
+        <v>420</v>
+      </c>
+      <c r="E88" s="12">
+        <v>120</v>
+      </c>
+      <c r="F88" s="12">
+        <v>250</v>
+      </c>
+      <c r="G88" s="12">
+        <v>5</v>
+      </c>
+      <c r="H88" s="12">
+        <v>30</v>
+      </c>
+      <c r="I88" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J88" s="13" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J88" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K88" s="14"/>
-      <c r="L88" s="14"/>
-      <c r="M88" s="14"/>
-      <c r="N88" s="15"/>
+        <v>290</v>
+      </c>
+      <c r="K88" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="L88" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="M88" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N88" s="15" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="89" spans="1:14">
       <c r="A89" s="11"/>

--- a/12623065.xlsx
+++ b/12623065.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="133">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -5664,26 +5664,50 @@
       </c>
     </row>
     <row r="89" spans="1:14">
-      <c r="A89" s="11"/>
-      <c r="B89" s="12"/>
-      <c r="C89" s="12"/>
-      <c r="D89" s="12"/>
-      <c r="E89" s="12"/>
-      <c r="F89" s="12"/>
-      <c r="G89" s="12"/>
-      <c r="H89" s="12"/>
-      <c r="I89" s="13" t="str">
+      <c r="A89" s="11">
+        <v>46326</v>
+      </c>
+      <c r="B89" s="12">
+        <v>300</v>
+      </c>
+      <c r="C89" s="12">
+        <v>30</v>
+      </c>
+      <c r="D89" s="12">
+        <v>360</v>
+      </c>
+      <c r="E89" s="12">
+        <v>120</v>
+      </c>
+      <c r="F89" s="12">
+        <v>100</v>
+      </c>
+      <c r="G89" s="12">
+        <v>2</v>
+      </c>
+      <c r="H89" s="12">
+        <v>30</v>
+      </c>
+      <c r="I89" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J89" s="13" t="str">
+        <v>940</v>
+      </c>
+      <c r="J89" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K89" s="14"/>
-      <c r="L89" s="14"/>
-      <c r="M89" s="14"/>
-      <c r="N89" s="15"/>
+        <v>500</v>
+      </c>
+      <c r="K89" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="L89" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="M89" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="N89" s="15" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="90" spans="1:14">
       <c r="A90" s="11"/>
@@ -12585,7 +12609,7 @@
     <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L401">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M401">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M87 M88:M89 M90:M401">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
   </dataValidations>
